--- a/research/traditional_assets/database/data/poland/poland_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_telecom_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1098186055692035</v>
+        <v>0.109646400218622</v>
       </c>
       <c r="C2">
-        <v>34.6</v>
+        <v>34.34427467585058</v>
       </c>
       <c r="D2">
-        <v>33.47</v>
+        <v>33.56027467585058</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="G2">
         <v>1.13</v>
@@ -1451,28 +1451,28 @@
         <v>0.509</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0174038</v>
       </c>
       <c r="N2">
-        <v>0.509</v>
+        <v>0.4915962</v>
       </c>
       <c r="O2">
-        <v>0.09671</v>
+        <v>0.09340327799999999</v>
       </c>
       <c r="P2">
-        <v>0.41229</v>
+        <v>0.398192922</v>
       </c>
       <c r="Q2">
-        <v>0.66029</v>
+        <v>0.646192922</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1098186055692035</v>
+        <v>0.1103423941602243</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.182116615397102</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>29.24648639952194</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.109646400218622</v>
+        <v>0.1094741948680406</v>
       </c>
       <c r="C3">
-        <v>34.34427467585058</v>
+        <v>34.08903764314279</v>
       </c>
       <c r="D3">
-        <v>33.56027467585058</v>
+        <v>33.65103764314279</v>
       </c>
       <c r="E3">
-        <v>0.346</v>
+        <v>0.6920000000000001</v>
       </c>
       <c r="F3">
-        <v>0.346</v>
+        <v>0.6920000000000001</v>
       </c>
       <c r="G3">
         <v>1.13</v>
@@ -1533,28 +1533,28 @@
         <v>0.509</v>
       </c>
       <c r="M3">
-        <v>0.0174038</v>
+        <v>0.0348076</v>
       </c>
       <c r="N3">
-        <v>0.4915962</v>
+        <v>0.4741924</v>
       </c>
       <c r="O3">
-        <v>0.09340327799999999</v>
+        <v>0.09009655600000001</v>
       </c>
       <c r="P3">
-        <v>0.398192922</v>
+        <v>0.384095844</v>
       </c>
       <c r="Q3">
-        <v>0.646192922</v>
+        <v>0.632095844</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1103423941602243</v>
+        <v>0.1108768723143271</v>
       </c>
       <c r="T3">
-        <v>1.182116615397102</v>
+        <v>1.19190577049047</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>29.24648639952194</v>
+        <v>14.62324319976097</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1094741948680406</v>
+        <v>0.1093797495174591</v>
       </c>
       <c r="C4">
-        <v>34.08903764314279</v>
+        <v>33.79302500659984</v>
       </c>
       <c r="D4">
-        <v>33.65103764314279</v>
+        <v>33.70102500659983</v>
       </c>
       <c r="E4">
-        <v>0.6920000000000001</v>
+        <v>1.038</v>
       </c>
       <c r="F4">
-        <v>0.6920000000000001</v>
+        <v>1.038</v>
       </c>
       <c r="G4">
         <v>1.13</v>
@@ -1615,45 +1615,45 @@
         <v>0.509</v>
       </c>
       <c r="M4">
-        <v>0.0348076</v>
+        <v>0.055533</v>
       </c>
       <c r="N4">
-        <v>0.4741924</v>
+        <v>0.453467</v>
       </c>
       <c r="O4">
-        <v>0.09009655600000001</v>
+        <v>0.08615873</v>
       </c>
       <c r="P4">
-        <v>0.384095844</v>
+        <v>0.36730827</v>
       </c>
       <c r="Q4">
-        <v>0.632095844</v>
+        <v>0.61530827</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1108768723143271</v>
+        <v>0.1114223706365557</v>
       </c>
       <c r="T4">
-        <v>1.19190577049047</v>
+        <v>1.201896763833185</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.19</v>
       </c>
       <c r="W4">
-        <v>0.040743</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>14.62324319976097</v>
+        <v>9.165721282840833</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1093797495174591</v>
+        <v>0.1092593841668776</v>
       </c>
       <c r="C5">
-        <v>33.79302500659984</v>
+        <v>33.51094676920642</v>
       </c>
       <c r="D5">
-        <v>33.70102500659983</v>
+        <v>33.76494676920642</v>
       </c>
       <c r="E5">
-        <v>1.038</v>
+        <v>1.384</v>
       </c>
       <c r="F5">
-        <v>1.038</v>
+        <v>1.384</v>
       </c>
       <c r="G5">
         <v>1.13</v>
@@ -1697,45 +1697,45 @@
         <v>0.509</v>
       </c>
       <c r="M5">
-        <v>0.055533</v>
+        <v>0.0751512</v>
       </c>
       <c r="N5">
-        <v>0.453467</v>
+        <v>0.4338488</v>
       </c>
       <c r="O5">
-        <v>0.08615873</v>
+        <v>0.08243127200000001</v>
       </c>
       <c r="P5">
-        <v>0.36730827</v>
+        <v>0.351417528</v>
       </c>
       <c r="Q5">
-        <v>0.61530827</v>
+        <v>0.599417528</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1114223706365557</v>
+        <v>0.1119792335071642</v>
       </c>
       <c r="T5">
-        <v>1.201896763833185</v>
+        <v>1.21209590287054</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0.19</v>
       </c>
       <c r="W5">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>9.165721282840833</v>
+        <v>6.773012273922439</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1092593841668776</v>
+        <v>0.1091600788162961</v>
       </c>
       <c r="C6">
-        <v>33.51094676920642</v>
+        <v>33.21786715596927</v>
       </c>
       <c r="D6">
-        <v>33.76494676920642</v>
+        <v>33.81786715596926</v>
       </c>
       <c r="E6">
-        <v>1.384</v>
+        <v>1.73</v>
       </c>
       <c r="F6">
-        <v>1.384</v>
+        <v>1.73</v>
       </c>
       <c r="G6">
         <v>1.13</v>
@@ -1779,45 +1779,45 @@
         <v>0.509</v>
       </c>
       <c r="M6">
-        <v>0.0751512</v>
+        <v>0.09566900000000002</v>
       </c>
       <c r="N6">
-        <v>0.4338488</v>
+        <v>0.413331</v>
       </c>
       <c r="O6">
-        <v>0.08243127200000001</v>
+        <v>0.07853289000000001</v>
       </c>
       <c r="P6">
-        <v>0.351417528</v>
+        <v>0.33479811</v>
       </c>
       <c r="Q6">
-        <v>0.599417528</v>
+        <v>0.5827981099999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1119792335071642</v>
+        <v>0.1125478198066275</v>
       </c>
       <c r="T6">
-        <v>1.21209590287054</v>
+        <v>1.222509760624472</v>
       </c>
       <c r="U6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.19</v>
       </c>
       <c r="W6">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.773012273922439</v>
+        <v>5.320427724759326</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1091600788162961</v>
+        <v>0.1091498734657146</v>
       </c>
       <c r="C7">
-        <v>33.21786715596927</v>
+        <v>32.87731504672836</v>
       </c>
       <c r="D7">
-        <v>33.81786715596926</v>
+        <v>33.82331504672835</v>
       </c>
       <c r="E7">
-        <v>1.73</v>
+        <v>2.076</v>
       </c>
       <c r="F7">
-        <v>1.73</v>
+        <v>2.076</v>
       </c>
       <c r="G7">
         <v>1.13</v>
@@ -1861,45 +1861,45 @@
         <v>0.509</v>
       </c>
       <c r="M7">
-        <v>0.09566900000000002</v>
+        <v>0.1199928</v>
       </c>
       <c r="N7">
-        <v>0.413331</v>
+        <v>0.3890072</v>
       </c>
       <c r="O7">
-        <v>0.07853289000000001</v>
+        <v>0.07391136800000001</v>
       </c>
       <c r="P7">
-        <v>0.33479811</v>
+        <v>0.315095832</v>
       </c>
       <c r="Q7">
-        <v>0.5827981099999999</v>
+        <v>0.563095832</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1125478198066275</v>
+        <v>0.1131285036869304</v>
       </c>
       <c r="T7">
-        <v>1.222509760624472</v>
+        <v>1.233145189819976</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V7">
         <v>0.19</v>
       </c>
       <c r="W7">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y7">
-        <v>5.320427724759326</v>
+        <v>4.241921181937583</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1091498734657146</v>
+        <v>0.1093956281151331</v>
       </c>
       <c r="C8">
-        <v>32.87731504672836</v>
+        <v>32.40061051281869</v>
       </c>
       <c r="D8">
-        <v>33.82331504672835</v>
+        <v>33.69261051281868</v>
       </c>
       <c r="E8">
-        <v>2.076</v>
+        <v>2.422</v>
       </c>
       <c r="F8">
-        <v>2.076</v>
+        <v>2.422</v>
       </c>
       <c r="G8">
         <v>1.13</v>
@@ -1943,45 +1943,45 @@
         <v>0.509</v>
       </c>
       <c r="M8">
-        <v>0.1199928</v>
+        <v>0.1552502</v>
       </c>
       <c r="N8">
-        <v>0.3890072</v>
+        <v>0.3537498</v>
       </c>
       <c r="O8">
-        <v>0.07391136800000001</v>
+        <v>0.067212462</v>
       </c>
       <c r="P8">
-        <v>0.315095832</v>
+        <v>0.286537338</v>
       </c>
       <c r="Q8">
-        <v>0.563095832</v>
+        <v>0.534537338</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1131285036869304</v>
+        <v>0.1137216753926163</v>
       </c>
       <c r="T8">
-        <v>1.233145189819976</v>
+        <v>1.244009337922911</v>
       </c>
       <c r="U8">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V8">
         <v>0.19</v>
       </c>
       <c r="W8">
-        <v>0.04681800000000001</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.241921181937583</v>
+        <v>3.278578707144983</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1093956281151331</v>
+        <v>0.1098406427645516</v>
       </c>
       <c r="C9">
-        <v>32.40061051281869</v>
+        <v>31.82048254957382</v>
       </c>
       <c r="D9">
-        <v>33.69261051281869</v>
+        <v>33.45848254957382</v>
       </c>
       <c r="E9">
-        <v>2.422</v>
+        <v>2.768</v>
       </c>
       <c r="F9">
-        <v>2.422</v>
+        <v>2.768</v>
       </c>
       <c r="G9">
         <v>1.13</v>
@@ -2025,45 +2025,45 @@
         <v>0.509</v>
       </c>
       <c r="M9">
-        <v>0.1552502</v>
+        <v>0.1990192</v>
       </c>
       <c r="N9">
-        <v>0.3537498</v>
+        <v>0.3099807999999999</v>
       </c>
       <c r="O9">
-        <v>0.067212462</v>
+        <v>0.05889635199999999</v>
       </c>
       <c r="P9">
-        <v>0.286537338</v>
+        <v>0.251084448</v>
       </c>
       <c r="Q9">
-        <v>0.534537338</v>
+        <v>0.499084448</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1137216753926163</v>
+        <v>0.1143277421353822</v>
       </c>
       <c r="T9">
-        <v>1.244009337922911</v>
+        <v>1.255109663158518</v>
       </c>
       <c r="U9">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V9">
         <v>0.19</v>
       </c>
       <c r="W9">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.278578707144982</v>
+        <v>2.557542186884481</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1098406427645516</v>
+        <v>0.1101277074139701</v>
       </c>
       <c r="C10">
-        <v>31.82048254957382</v>
+        <v>31.32517289826979</v>
       </c>
       <c r="D10">
-        <v>33.45848254957382</v>
+        <v>33.30917289826979</v>
       </c>
       <c r="E10">
-        <v>2.768</v>
+        <v>3.114</v>
       </c>
       <c r="F10">
-        <v>2.768</v>
+        <v>3.114</v>
       </c>
       <c r="G10">
         <v>1.13</v>
@@ -2107,45 +2107,45 @@
         <v>0.509</v>
       </c>
       <c r="M10">
-        <v>0.1990192</v>
+        <v>0.2360412</v>
       </c>
       <c r="N10">
-        <v>0.3099807999999999</v>
+        <v>0.2729588</v>
       </c>
       <c r="O10">
-        <v>0.05889635199999999</v>
+        <v>0.051862172</v>
       </c>
       <c r="P10">
-        <v>0.251084448</v>
+        <v>0.221096628</v>
       </c>
       <c r="Q10">
-        <v>0.499084448</v>
+        <v>0.469096628</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1143277421353822</v>
+        <v>0.1149471290263408</v>
       </c>
       <c r="T10">
-        <v>1.255109663158518</v>
+        <v>1.266453951586116</v>
       </c>
       <c r="U10">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V10">
         <v>0.19</v>
       </c>
       <c r="W10">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.557542186884481</v>
+        <v>2.156403204186388</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,81 +2153,81 @@
     </row>
     <row r="11">
       <c r="A11">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="B11">
+        <v>0.1113122520633887</v>
+      </c>
+      <c r="C11">
+        <v>30.37690078442113</v>
+      </c>
+      <c r="D11">
+        <v>32.70690078442113</v>
+      </c>
+      <c r="E11">
+        <v>3.46</v>
+      </c>
+      <c r="F11">
+        <v>3.46</v>
+      </c>
+      <c r="G11">
+        <v>1.13</v>
+      </c>
+      <c r="H11">
+        <v>34.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.757</v>
+      </c>
+      <c r="K11">
+        <v>0.248</v>
+      </c>
+      <c r="L11">
+        <v>0.509</v>
+      </c>
+      <c r="M11">
+        <v>0.3114</v>
+      </c>
+      <c r="N11">
+        <v>0.1976</v>
+      </c>
+      <c r="O11">
+        <v>0.037544</v>
+      </c>
+      <c r="P11">
+        <v>0.160056</v>
+      </c>
+      <c r="Q11">
+        <v>0.408056</v>
+      </c>
+      <c r="R11">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S11">
+        <v>0.1155802800704319</v>
+      </c>
+      <c r="T11">
+        <v>1.278050335312106</v>
+      </c>
+      <c r="U11">
         <v>0.09</v>
-      </c>
-      <c r="B11">
-        <v>0.1101277074139701</v>
-      </c>
-      <c r="C11">
-        <v>31.32517289826979</v>
-      </c>
-      <c r="D11">
-        <v>33.30917289826979</v>
-      </c>
-      <c r="E11">
-        <v>3.114</v>
-      </c>
-      <c r="F11">
-        <v>3.114</v>
-      </c>
-      <c r="G11">
-        <v>1.13</v>
-      </c>
-      <c r="H11">
-        <v>34.6</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0.757</v>
-      </c>
-      <c r="K11">
-        <v>0.248</v>
-      </c>
-      <c r="L11">
-        <v>0.509</v>
-      </c>
-      <c r="M11">
-        <v>0.2360412</v>
-      </c>
-      <c r="N11">
-        <v>0.2729588</v>
-      </c>
-      <c r="O11">
-        <v>0.051862172</v>
-      </c>
-      <c r="P11">
-        <v>0.221096628</v>
-      </c>
-      <c r="Q11">
-        <v>0.469096628</v>
-      </c>
-      <c r="R11">
-        <v>0.0989010989010989</v>
-      </c>
-      <c r="S11">
-        <v>0.1149471290263408</v>
-      </c>
-      <c r="T11">
-        <v>1.266453951586116</v>
-      </c>
-      <c r="U11">
-        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.19</v>
       </c>
       <c r="W11">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.156403204186388</v>
+        <v>1.634553628773282</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1113122520633887</v>
+        <v>0.1169145982011125</v>
       </c>
       <c r="C12">
-        <v>30.37690078442113</v>
+        <v>27.45427961350028</v>
       </c>
       <c r="D12">
-        <v>32.70690078442113</v>
+        <v>30.13027961350028</v>
       </c>
       <c r="E12">
-        <v>3.46</v>
+        <v>3.806</v>
       </c>
       <c r="F12">
-        <v>3.46</v>
+        <v>3.806</v>
       </c>
       <c r="G12">
         <v>1.13</v>
@@ -2271,45 +2271,45 @@
         <v>0.509</v>
       </c>
       <c r="M12">
-        <v>0.3114</v>
+        <v>0.5587208</v>
       </c>
       <c r="N12">
-        <v>0.1976</v>
+        <v>-0.04972080000000001</v>
       </c>
       <c r="O12">
-        <v>0.037544</v>
+        <v>-0.009446952000000002</v>
       </c>
       <c r="P12">
-        <v>0.160056</v>
+        <v>-0.04027384800000001</v>
       </c>
       <c r="Q12">
-        <v>0.408056</v>
+        <v>0.207726152</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1155802800704319</v>
+        <v>0.1163614437149604</v>
       </c>
       <c r="T12">
-        <v>1.278050335312106</v>
+        <v>1.292357621794987</v>
       </c>
       <c r="U12">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V12">
-        <v>0.19</v>
+        <v>0.1730918197425262</v>
       </c>
       <c r="W12">
-        <v>0.07290000000000001</v>
+        <v>0.1213901208617972</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y12">
-        <v>1.634553628773282</v>
+        <v>0.9110095775922429</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1169145982011125</v>
+        <v>0.1179245982011125</v>
       </c>
       <c r="C13">
-        <v>27.45427961350028</v>
+        <v>26.68634891067986</v>
       </c>
       <c r="D13">
-        <v>30.13027961350028</v>
+        <v>29.70834891067986</v>
       </c>
       <c r="E13">
-        <v>3.806</v>
+        <v>4.152</v>
       </c>
       <c r="F13">
-        <v>3.806</v>
+        <v>4.152</v>
       </c>
       <c r="G13">
         <v>1.13</v>
@@ -2353,37 +2353,37 @@
         <v>0.509</v>
       </c>
       <c r="M13">
-        <v>0.5587208</v>
+        <v>0.6095136000000001</v>
       </c>
       <c r="N13">
-        <v>-0.04972080000000001</v>
+        <v>-0.1005136000000001</v>
       </c>
       <c r="O13">
-        <v>-0.009446952000000002</v>
+        <v>-0.01909758400000002</v>
       </c>
       <c r="P13">
-        <v>-0.04027384800000001</v>
+        <v>-0.08141601600000008</v>
       </c>
       <c r="Q13">
-        <v>0.207726152</v>
+        <v>0.1665839839999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1163614437149604</v>
+        <v>0.1171632783026304</v>
       </c>
       <c r="T13">
-        <v>1.292357621794987</v>
+        <v>1.307043503860839</v>
       </c>
       <c r="U13">
         <v>0.1468</v>
       </c>
       <c r="V13">
-        <v>0.1730918197425262</v>
+        <v>0.1586675014306489</v>
       </c>
       <c r="W13">
-        <v>0.1213901208617972</v>
+        <v>0.1235076107899808</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.9110095775922429</v>
+        <v>0.8350921127928892</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1179245982011125</v>
+        <v>0.1262823955905347</v>
       </c>
       <c r="C14">
-        <v>26.68634891067986</v>
+        <v>23.2552473906783</v>
       </c>
       <c r="D14">
-        <v>29.70834891067986</v>
+        <v>26.6232473906783</v>
       </c>
       <c r="E14">
-        <v>4.152</v>
+        <v>4.498</v>
       </c>
       <c r="F14">
-        <v>4.152</v>
+        <v>4.498</v>
       </c>
       <c r="G14">
         <v>1.13</v>
@@ -2435,45 +2435,45 @@
         <v>0.509</v>
       </c>
       <c r="M14">
-        <v>0.6095136000000001</v>
+        <v>0.9031984000000001</v>
       </c>
       <c r="N14">
-        <v>-0.1005136000000001</v>
+        <v>-0.3941984000000001</v>
       </c>
       <c r="O14">
-        <v>-0.01909758400000002</v>
+        <v>-0.07489769600000001</v>
       </c>
       <c r="P14">
-        <v>-0.08141601600000008</v>
+        <v>-0.319300704</v>
       </c>
       <c r="Q14">
-        <v>0.1665839839999999</v>
+        <v>-0.07130070400000005</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1171632783026304</v>
+        <v>0.1183603244778587</v>
       </c>
       <c r="T14">
-        <v>1.307043503860839</v>
+        <v>1.328967824945397</v>
       </c>
       <c r="U14">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.1586675014306489</v>
+        <v>0.1070750346767665</v>
       </c>
       <c r="W14">
-        <v>0.1235076107899808</v>
+        <v>0.1792993330369053</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.8350921127928892</v>
+        <v>0.5635528140882446</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1262823955905347</v>
+        <v>0.1278323955905347</v>
       </c>
       <c r="C15">
-        <v>23.2552473906783</v>
+        <v>22.4062018175424</v>
       </c>
       <c r="D15">
-        <v>26.6232473906783</v>
+        <v>26.1202018175424</v>
       </c>
       <c r="E15">
-        <v>4.498</v>
+        <v>4.844</v>
       </c>
       <c r="F15">
-        <v>4.498</v>
+        <v>4.844</v>
       </c>
       <c r="G15">
         <v>1.13</v>
@@ -2517,37 +2517,37 @@
         <v>0.509</v>
       </c>
       <c r="M15">
-        <v>0.9031984000000001</v>
+        <v>0.9726752000000001</v>
       </c>
       <c r="N15">
-        <v>-0.3941984000000001</v>
+        <v>-0.4636752000000001</v>
       </c>
       <c r="O15">
-        <v>-0.07489769600000001</v>
+        <v>-0.08809828800000001</v>
       </c>
       <c r="P15">
-        <v>-0.319300704</v>
+        <v>-0.375576912</v>
       </c>
       <c r="Q15">
-        <v>-0.07130070400000005</v>
+        <v>-0.127576912</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1183603244778587</v>
+        <v>0.1192040491810896</v>
       </c>
       <c r="T15">
-        <v>1.328967824945397</v>
+        <v>1.344420939188948</v>
       </c>
       <c r="U15">
         <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.1070750346767665</v>
+        <v>0.09942681791414029</v>
       </c>
       <c r="W15">
-        <v>0.1792993330369053</v>
+        <v>0.1808350949628406</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.5635528140882446</v>
+        <v>0.52329904165337</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1278323955905347</v>
+        <v>0.13476466579652</v>
       </c>
       <c r="C16">
-        <v>22.4062018175424</v>
+        <v>20.02487357556124</v>
       </c>
       <c r="D16">
-        <v>26.1202018175424</v>
+        <v>24.08487357556124</v>
       </c>
       <c r="E16">
-        <v>4.844</v>
+        <v>5.190000000000001</v>
       </c>
       <c r="F16">
-        <v>4.844</v>
+        <v>5.190000000000001</v>
       </c>
       <c r="G16">
         <v>1.13</v>
@@ -2599,45 +2599,45 @@
         <v>0.509</v>
       </c>
       <c r="M16">
-        <v>0.9726752000000001</v>
+        <v>1.223802</v>
       </c>
       <c r="N16">
-        <v>-0.4636752000000001</v>
+        <v>-0.7148020000000003</v>
       </c>
       <c r="O16">
-        <v>-0.08809828800000001</v>
+        <v>-0.1358123800000001</v>
       </c>
       <c r="P16">
-        <v>-0.375576912</v>
+        <v>-0.5789896200000002</v>
       </c>
       <c r="Q16">
-        <v>-0.127576912</v>
+        <v>-0.3309896200000002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1192040491810896</v>
+        <v>0.1202232382373204</v>
       </c>
       <c r="T16">
-        <v>1.344420939188948</v>
+        <v>1.363087744678228</v>
       </c>
       <c r="U16">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.09942681791414029</v>
+        <v>0.07902422123840293</v>
       </c>
       <c r="W16">
-        <v>0.1808350949628406</v>
+        <v>0.2171660886319846</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.52329904165337</v>
+        <v>0.4159169538863312</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.13476466579652</v>
+        <v>0.13666466579652</v>
       </c>
       <c r="C17">
-        <v>20.02487357556126</v>
+        <v>19.17525361072208</v>
       </c>
       <c r="D17">
-        <v>24.08487357556126</v>
+        <v>23.58125361072208</v>
       </c>
       <c r="E17">
-        <v>5.19</v>
+        <v>5.536</v>
       </c>
       <c r="F17">
-        <v>5.19</v>
+        <v>5.536</v>
       </c>
       <c r="G17">
         <v>1.13</v>
@@ -2681,37 +2681,37 @@
         <v>0.509</v>
       </c>
       <c r="M17">
-        <v>1.223802</v>
+        <v>1.3053888</v>
       </c>
       <c r="N17">
-        <v>-0.714802</v>
+        <v>-0.7963888000000002</v>
       </c>
       <c r="O17">
-        <v>-0.13581238</v>
+        <v>-0.151313872</v>
       </c>
       <c r="P17">
-        <v>-0.57898962</v>
+        <v>-0.6450749280000002</v>
       </c>
       <c r="Q17">
-        <v>-0.33098962</v>
+        <v>-0.3970749280000002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1202232382373203</v>
+        <v>0.121109229168717</v>
       </c>
       <c r="T17">
-        <v>1.363087744678227</v>
+        <v>1.379314979733921</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.07902422123840294</v>
+        <v>0.07408520741100275</v>
       </c>
       <c r="W17">
-        <v>0.2171660886319846</v>
+        <v>0.2183307080924856</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.4159169538863313</v>
+        <v>0.3899221442684355</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.13666466579652</v>
+        <v>0.13856466579652</v>
       </c>
       <c r="C18">
-        <v>19.17525361072208</v>
+        <v>18.34626387022486</v>
       </c>
       <c r="D18">
-        <v>23.58125361072208</v>
+        <v>23.09826387022487</v>
       </c>
       <c r="E18">
-        <v>5.536</v>
+        <v>5.882000000000001</v>
       </c>
       <c r="F18">
-        <v>5.536</v>
+        <v>5.882000000000001</v>
       </c>
       <c r="G18">
         <v>1.13</v>
@@ -2763,37 +2763,37 @@
         <v>0.509</v>
       </c>
       <c r="M18">
-        <v>1.3053888</v>
+        <v>1.3869756</v>
       </c>
       <c r="N18">
-        <v>-0.7963888000000002</v>
+        <v>-0.8779756000000002</v>
       </c>
       <c r="O18">
-        <v>-0.151313872</v>
+        <v>-0.166815364</v>
       </c>
       <c r="P18">
-        <v>-0.6450749280000002</v>
+        <v>-0.7111602360000001</v>
       </c>
       <c r="Q18">
-        <v>-0.3970749280000002</v>
+        <v>-0.4631602360000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.121109229168717</v>
+        <v>0.1220165692791835</v>
       </c>
       <c r="T18">
-        <v>1.379314979733921</v>
+        <v>1.395933232501799</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.07408520741100275</v>
+        <v>0.06972725403388495</v>
       </c>
       <c r="W18">
-        <v>0.2183307080924856</v>
+        <v>0.2193583134988099</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3899221442684355</v>
+        <v>0.3669855475467628</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.13856466579652</v>
+        <v>0.14046466579652</v>
       </c>
       <c r="C19">
-        <v>18.34626387022486</v>
+        <v>17.53666215585594</v>
       </c>
       <c r="D19">
-        <v>23.09826387022487</v>
+        <v>22.63466215585595</v>
       </c>
       <c r="E19">
-        <v>5.882000000000001</v>
+        <v>6.228000000000001</v>
       </c>
       <c r="F19">
-        <v>5.882000000000001</v>
+        <v>6.228000000000001</v>
       </c>
       <c r="G19">
         <v>1.13</v>
@@ -2845,37 +2845,37 @@
         <v>0.509</v>
       </c>
       <c r="M19">
-        <v>1.3869756</v>
+        <v>1.4685624</v>
       </c>
       <c r="N19">
-        <v>-0.8779756000000002</v>
+        <v>-0.9595624000000001</v>
       </c>
       <c r="O19">
-        <v>-0.166815364</v>
+        <v>-0.182316856</v>
       </c>
       <c r="P19">
-        <v>-0.7111602360000001</v>
+        <v>-0.7772455440000001</v>
       </c>
       <c r="Q19">
-        <v>-0.4631602360000001</v>
+        <v>-0.5292455440000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1220165692791835</v>
+        <v>0.1229460396362467</v>
       </c>
       <c r="T19">
-        <v>1.395933232501799</v>
+        <v>1.412956808507919</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.06972725403388495</v>
+        <v>0.06585351769866911</v>
       </c>
       <c r="W19">
-        <v>0.2193583134988099</v>
+        <v>0.2202717405266538</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3669855475467628</v>
+        <v>0.3465974615719427</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.14046466579652</v>
+        <v>0.14236466579652</v>
       </c>
       <c r="C20">
-        <v>17.53666215585594</v>
+        <v>16.74530403504239</v>
       </c>
       <c r="D20">
-        <v>22.63466215585595</v>
+        <v>22.18930403504239</v>
       </c>
       <c r="E20">
-        <v>6.228</v>
+        <v>6.574000000000001</v>
       </c>
       <c r="F20">
-        <v>6.228</v>
+        <v>6.574000000000001</v>
       </c>
       <c r="G20">
         <v>1.13</v>
@@ -2927,37 +2927,37 @@
         <v>0.509</v>
       </c>
       <c r="M20">
-        <v>1.4685624</v>
+        <v>1.5501492</v>
       </c>
       <c r="N20">
-        <v>-0.9595623999999999</v>
+        <v>-1.0411492</v>
       </c>
       <c r="O20">
-        <v>-0.182316856</v>
+        <v>-0.1978183480000001</v>
       </c>
       <c r="P20">
-        <v>-0.7772455439999999</v>
+        <v>-0.8433308520000004</v>
       </c>
       <c r="Q20">
-        <v>-0.5292455439999999</v>
+        <v>-0.5953308520000004</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1229460396362467</v>
+        <v>0.1238984598786695</v>
       </c>
       <c r="T20">
-        <v>1.412956808507919</v>
+        <v>1.430400719724066</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.06585351769866912</v>
+        <v>0.06238754308294968</v>
       </c>
       <c r="W20">
-        <v>0.2202717405266538</v>
+        <v>0.2210890173410405</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3465974615719427</v>
+        <v>0.3283554899102614</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.14236466579652</v>
+        <v>0.14426466579652</v>
       </c>
       <c r="C21">
-        <v>16.74530403504239</v>
+        <v>15.97113340829489</v>
       </c>
       <c r="D21">
-        <v>22.18930403504239</v>
+        <v>21.76113340829489</v>
       </c>
       <c r="E21">
-        <v>6.574000000000001</v>
+        <v>6.920000000000001</v>
       </c>
       <c r="F21">
-        <v>6.574000000000001</v>
+        <v>6.920000000000001</v>
       </c>
       <c r="G21">
         <v>1.13</v>
@@ -3009,37 +3009,37 @@
         <v>0.509</v>
       </c>
       <c r="M21">
-        <v>1.5501492</v>
+        <v>1.631736</v>
       </c>
       <c r="N21">
-        <v>-1.0411492</v>
+        <v>-1.122736</v>
       </c>
       <c r="O21">
-        <v>-0.1978183480000001</v>
+        <v>-0.21331984</v>
       </c>
       <c r="P21">
-        <v>-0.8433308520000004</v>
+        <v>-0.9094161600000001</v>
       </c>
       <c r="Q21">
-        <v>-0.5953308520000004</v>
+        <v>-0.6614161600000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1238984598786695</v>
+        <v>0.1248746906271529</v>
       </c>
       <c r="T21">
-        <v>1.430400719724066</v>
+        <v>1.448280728720617</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.06238754308294968</v>
+        <v>0.0592681659288022</v>
       </c>
       <c r="W21">
-        <v>0.2210890173410405</v>
+        <v>0.2218245664739884</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3283554899102614</v>
+        <v>0.3119377154147485</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.14426466579652</v>
+        <v>0.14616466579652</v>
       </c>
       <c r="C22">
-        <v>15.97113340829489</v>
+        <v>15.21317414805496</v>
       </c>
       <c r="D22">
-        <v>21.76113340829489</v>
+        <v>21.34917414805497</v>
       </c>
       <c r="E22">
-        <v>6.920000000000001</v>
+        <v>7.266000000000001</v>
       </c>
       <c r="F22">
-        <v>6.920000000000001</v>
+        <v>7.266000000000001</v>
       </c>
       <c r="G22">
         <v>1.13</v>
@@ -3091,37 +3091,37 @@
         <v>0.509</v>
       </c>
       <c r="M22">
-        <v>1.631736</v>
+        <v>1.7133228</v>
       </c>
       <c r="N22">
-        <v>-1.122736</v>
+        <v>-1.2043228</v>
       </c>
       <c r="O22">
-        <v>-0.21331984</v>
+        <v>-0.2288213320000001</v>
       </c>
       <c r="P22">
-        <v>-0.9094161600000001</v>
+        <v>-0.9755014680000003</v>
       </c>
       <c r="Q22">
-        <v>-0.6614161600000001</v>
+        <v>-0.7275014680000003</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1248746906271529</v>
+        <v>0.1258756360781295</v>
       </c>
       <c r="T22">
-        <v>1.448280728720617</v>
+        <v>1.466613396172777</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.0592681659288022</v>
+        <v>0.05644587231314496</v>
       </c>
       <c r="W22">
-        <v>0.2218245664739884</v>
+        <v>0.2224900633085604</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3119377154147485</v>
+        <v>0.2970835384902365</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.14616466579652</v>
+        <v>0.14806466579652</v>
       </c>
       <c r="C23">
-        <v>15.21317414805497</v>
+        <v>14.47052266960576</v>
       </c>
       <c r="D23">
-        <v>21.34917414805497</v>
+        <v>20.95252266960576</v>
       </c>
       <c r="E23">
-        <v>7.266</v>
+        <v>7.612</v>
       </c>
       <c r="F23">
-        <v>7.266</v>
+        <v>7.612</v>
       </c>
       <c r="G23">
         <v>1.13</v>
@@ -3173,37 +3173,37 @@
         <v>0.509</v>
       </c>
       <c r="M23">
-        <v>1.7133228</v>
+        <v>1.7949096</v>
       </c>
       <c r="N23">
-        <v>-1.2043228</v>
+        <v>-1.2859096</v>
       </c>
       <c r="O23">
-        <v>-0.228821332</v>
+        <v>-0.244322824</v>
       </c>
       <c r="P23">
-        <v>-0.9755014679999999</v>
+        <v>-1.041586776</v>
       </c>
       <c r="Q23">
-        <v>-0.7275014679999999</v>
+        <v>-0.7935867760000002</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1258756360781295</v>
+        <v>0.1269022467970799</v>
       </c>
       <c r="T23">
-        <v>1.466613396172777</v>
+        <v>1.485416132021145</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05644587231314496</v>
+        <v>0.05388015084436564</v>
       </c>
       <c r="W23">
-        <v>0.2224900633085604</v>
+        <v>0.2230950604308986</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2970835384902367</v>
+        <v>0.2835797412861349</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.14806466579652</v>
+        <v>0.14996466579652</v>
       </c>
       <c r="C24">
-        <v>14.47052266960576</v>
+        <v>13.74234131503762</v>
       </c>
       <c r="D24">
-        <v>20.95252266960576</v>
+        <v>20.57034131503763</v>
       </c>
       <c r="E24">
-        <v>7.612</v>
+        <v>7.958000000000001</v>
       </c>
       <c r="F24">
-        <v>7.612</v>
+        <v>7.958000000000001</v>
       </c>
       <c r="G24">
         <v>1.13</v>
@@ -3255,37 +3255,37 @@
         <v>0.509</v>
       </c>
       <c r="M24">
-        <v>1.7949096</v>
+        <v>1.8764964</v>
       </c>
       <c r="N24">
-        <v>-1.2859096</v>
+        <v>-1.3674964</v>
       </c>
       <c r="O24">
-        <v>-0.244322824</v>
+        <v>-0.2598243160000001</v>
       </c>
       <c r="P24">
-        <v>-1.041586776</v>
+        <v>-1.107672084</v>
       </c>
       <c r="Q24">
-        <v>-0.7935867760000002</v>
+        <v>-0.8596720840000003</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1269022467970799</v>
+        <v>0.1279555227295095</v>
       </c>
       <c r="T24">
-        <v>1.485416132021145</v>
+        <v>1.504707250618823</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.05388015084436564</v>
+        <v>0.05153753559026279</v>
       </c>
       <c r="W24">
-        <v>0.2230950604308986</v>
+        <v>0.2236474491078161</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2835797412861349</v>
+        <v>0.2712501873171725</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.14996466579652</v>
+        <v>0.15186466579652</v>
       </c>
       <c r="C25">
-        <v>13.74234131503762</v>
+        <v>13.02785244831596</v>
       </c>
       <c r="D25">
-        <v>20.57034131503763</v>
+        <v>20.20185244831596</v>
       </c>
       <c r="E25">
-        <v>7.958000000000001</v>
+        <v>8.304</v>
       </c>
       <c r="F25">
-        <v>7.958000000000001</v>
+        <v>8.304</v>
       </c>
       <c r="G25">
         <v>1.13</v>
@@ -3337,37 +3337,37 @@
         <v>0.509</v>
       </c>
       <c r="M25">
-        <v>1.8764964</v>
+        <v>1.9580832</v>
       </c>
       <c r="N25">
-        <v>-1.3674964</v>
+        <v>-1.4490832</v>
       </c>
       <c r="O25">
-        <v>-0.2598243160000001</v>
+        <v>-0.275325808</v>
       </c>
       <c r="P25">
-        <v>-1.107672084</v>
+        <v>-1.173757392</v>
       </c>
       <c r="Q25">
-        <v>-0.8596720840000003</v>
+        <v>-0.925757392</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1279555227295095</v>
+        <v>0.1290365164496346</v>
       </c>
       <c r="T25">
-        <v>1.504707250618823</v>
+        <v>1.524506030232228</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05153753559026279</v>
+        <v>0.04939013827400184</v>
       </c>
       <c r="W25">
-        <v>0.2236474491078161</v>
+        <v>0.2241538053949904</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2712501873171725</v>
+        <v>0.2599480961789571</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.15186466579652</v>
+        <v>0.15376466579652</v>
       </c>
       <c r="C26">
-        <v>13.02785244831597</v>
+        <v>12.32633317385128</v>
       </c>
       <c r="D26">
-        <v>20.20185244831597</v>
+        <v>19.84633317385128</v>
       </c>
       <c r="E26">
-        <v>8.304</v>
+        <v>8.65</v>
       </c>
       <c r="F26">
-        <v>8.304</v>
+        <v>8.65</v>
       </c>
       <c r="G26">
         <v>1.13</v>
@@ -3419,37 +3419,37 @@
         <v>0.509</v>
       </c>
       <c r="M26">
-        <v>1.9580832</v>
+        <v>2.03967</v>
       </c>
       <c r="N26">
-        <v>-1.4490832</v>
+        <v>-1.53067</v>
       </c>
       <c r="O26">
-        <v>-0.275325808</v>
+        <v>-0.2908273000000001</v>
       </c>
       <c r="P26">
-        <v>-1.173757392</v>
+        <v>-1.2398427</v>
       </c>
       <c r="Q26">
-        <v>-0.925757392</v>
+        <v>-0.9918427000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1290365164496346</v>
+        <v>0.1301463366689631</v>
       </c>
       <c r="T26">
-        <v>1.524506030232228</v>
+        <v>1.544832777301991</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.04939013827400184</v>
+        <v>0.04741453274304177</v>
       </c>
       <c r="W26">
-        <v>0.2241538053949904</v>
+        <v>0.2246196531791908</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2599480961789571</v>
+        <v>0.2495501723317987</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.15376466579652</v>
+        <v>0.15566466579652</v>
       </c>
       <c r="C27">
-        <v>12.32633317385128</v>
+        <v>11.63711060309176</v>
       </c>
       <c r="D27">
-        <v>19.84633317385128</v>
+        <v>19.50311060309176</v>
       </c>
       <c r="E27">
-        <v>8.65</v>
+        <v>8.996</v>
       </c>
       <c r="F27">
-        <v>8.65</v>
+        <v>8.996</v>
       </c>
       <c r="G27">
         <v>1.13</v>
@@ -3501,37 +3501,37 @@
         <v>0.509</v>
       </c>
       <c r="M27">
-        <v>2.03967</v>
+        <v>2.1212568</v>
       </c>
       <c r="N27">
-        <v>-1.53067</v>
+        <v>-1.6122568</v>
       </c>
       <c r="O27">
-        <v>-0.2908273000000001</v>
+        <v>-0.3063287920000001</v>
       </c>
       <c r="P27">
-        <v>-1.2398427</v>
+        <v>-1.305928008</v>
       </c>
       <c r="Q27">
-        <v>-0.9918427000000001</v>
+        <v>-1.057928008</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1301463366689631</v>
+        <v>0.1312861520293545</v>
       </c>
       <c r="T27">
-        <v>1.544832777301991</v>
+        <v>1.56570889591418</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04741453274304177</v>
+        <v>0.04559089686830939</v>
       </c>
       <c r="W27">
-        <v>0.2246196531791908</v>
+        <v>0.2250496665184527</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2495501723317987</v>
+        <v>0.2399520887805756</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.15566466579652</v>
+        <v>0.15756466579652</v>
       </c>
       <c r="C28">
-        <v>11.63711060309176</v>
+        <v>10.95955760392351</v>
       </c>
       <c r="D28">
-        <v>19.50311060309176</v>
+        <v>19.17155760392351</v>
       </c>
       <c r="E28">
-        <v>8.996</v>
+        <v>9.342000000000001</v>
       </c>
       <c r="F28">
-        <v>8.996</v>
+        <v>9.342000000000001</v>
       </c>
       <c r="G28">
         <v>1.13</v>
@@ -3583,37 +3583,37 @@
         <v>0.509</v>
       </c>
       <c r="M28">
-        <v>2.1212568</v>
+        <v>2.2028436</v>
       </c>
       <c r="N28">
-        <v>-1.6122568</v>
+        <v>-1.6938436</v>
       </c>
       <c r="O28">
-        <v>-0.3063287920000001</v>
+        <v>-0.321830284</v>
       </c>
       <c r="P28">
-        <v>-1.305928008</v>
+        <v>-1.372013316</v>
       </c>
       <c r="Q28">
-        <v>-1.057928008</v>
+        <v>-1.124013316</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1312861520293545</v>
+        <v>0.1324571952078388</v>
       </c>
       <c r="T28">
-        <v>1.56570889591418</v>
+        <v>1.587156962981498</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04559089686830939</v>
+        <v>0.04390234513244608</v>
       </c>
       <c r="W28">
-        <v>0.2250496665184527</v>
+        <v>0.2254478270177692</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2399520887805756</v>
+        <v>0.2310649743812951</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.15756466579652</v>
+        <v>0.15946466579652</v>
       </c>
       <c r="C29">
-        <v>10.95955760392351</v>
+        <v>10.29308897638481</v>
       </c>
       <c r="D29">
-        <v>19.17155760392351</v>
+        <v>18.85108897638481</v>
       </c>
       <c r="E29">
-        <v>9.342000000000001</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="F29">
-        <v>9.342000000000001</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="G29">
         <v>1.13</v>
@@ -3665,37 +3665,37 @@
         <v>0.509</v>
       </c>
       <c r="M29">
-        <v>2.2028436</v>
+        <v>2.2844304</v>
       </c>
       <c r="N29">
-        <v>-1.6938436</v>
+        <v>-1.7754304</v>
       </c>
       <c r="O29">
-        <v>-0.321830284</v>
+        <v>-0.3373317760000001</v>
       </c>
       <c r="P29">
-        <v>-1.372013316</v>
+        <v>-1.438098624</v>
       </c>
       <c r="Q29">
-        <v>-1.124013316</v>
+        <v>-1.190098624</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1324571952078388</v>
+        <v>0.1336607673635032</v>
       </c>
       <c r="T29">
-        <v>1.587156962981498</v>
+        <v>1.609200809689574</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04390234513244608</v>
+        <v>0.04233440423485871</v>
       </c>
       <c r="W29">
-        <v>0.2254478270177692</v>
+        <v>0.2258175474814203</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2310649743812951</v>
+        <v>0.2228126538676775</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.15946466579652</v>
+        <v>0.16136466579652</v>
       </c>
       <c r="C30">
-        <v>10.29308897638481</v>
+        <v>9.637158005631203</v>
       </c>
       <c r="D30">
-        <v>18.85108897638481</v>
+        <v>18.54115800563121</v>
       </c>
       <c r="E30">
-        <v>9.688000000000001</v>
+        <v>10.034</v>
       </c>
       <c r="F30">
-        <v>9.688000000000001</v>
+        <v>10.034</v>
       </c>
       <c r="G30">
         <v>1.13</v>
@@ -3747,37 +3747,37 @@
         <v>0.509</v>
       </c>
       <c r="M30">
-        <v>2.2844304</v>
+        <v>2.366017200000001</v>
       </c>
       <c r="N30">
-        <v>-1.7754304</v>
+        <v>-1.857017200000001</v>
       </c>
       <c r="O30">
-        <v>-0.3373317760000001</v>
+        <v>-0.3528332680000002</v>
       </c>
       <c r="P30">
-        <v>-1.438098624</v>
+        <v>-1.504183932000001</v>
       </c>
       <c r="Q30">
-        <v>-1.190098624</v>
+        <v>-1.256183932000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1336607673635032</v>
+        <v>0.1348982429601723</v>
       </c>
       <c r="T30">
-        <v>1.609200809689574</v>
+        <v>1.631865609826047</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04233440423485871</v>
+        <v>0.04087459719227737</v>
       </c>
       <c r="W30">
-        <v>0.2258175474814203</v>
+        <v>0.226161769982061</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2228126538676775</v>
+        <v>0.215129458906723</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.16136466579652</v>
+        <v>0.16326466579652</v>
       </c>
       <c r="C31">
-        <v>9.637158005631214</v>
+        <v>8.991253349436777</v>
       </c>
       <c r="D31">
-        <v>18.54115800563121</v>
+        <v>18.24125334943678</v>
       </c>
       <c r="E31">
-        <v>10.034</v>
+        <v>10.38</v>
       </c>
       <c r="F31">
-        <v>10.034</v>
+        <v>10.38</v>
       </c>
       <c r="G31">
         <v>1.13</v>
@@ -3829,37 +3829,37 @@
         <v>0.509</v>
       </c>
       <c r="M31">
-        <v>2.3660172</v>
+        <v>2.447604</v>
       </c>
       <c r="N31">
-        <v>-1.8570172</v>
+        <v>-1.938604</v>
       </c>
       <c r="O31">
-        <v>-0.352833268</v>
+        <v>-0.36833476</v>
       </c>
       <c r="P31">
-        <v>-1.504183932</v>
+        <v>-1.57026924</v>
       </c>
       <c r="Q31">
-        <v>-1.256183932</v>
+        <v>-1.32226924</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1348982429601722</v>
+        <v>0.1361710750024605</v>
       </c>
       <c r="T31">
-        <v>1.631865609826047</v>
+        <v>1.655177975680705</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04087459719227739</v>
+        <v>0.03951211061920147</v>
       </c>
       <c r="W31">
-        <v>0.226161769982061</v>
+        <v>0.2264830443159923</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2151294589067231</v>
+        <v>0.2079584769431656</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.16326466579652</v>
+        <v>0.16516466579652</v>
       </c>
       <c r="C32">
-        <v>8.991253349436777</v>
+        <v>8.354896222956716</v>
       </c>
       <c r="D32">
-        <v>18.24125334943678</v>
+        <v>17.95089622295672</v>
       </c>
       <c r="E32">
-        <v>10.38</v>
+        <v>10.726</v>
       </c>
       <c r="F32">
-        <v>10.38</v>
+        <v>10.726</v>
       </c>
       <c r="G32">
         <v>1.13</v>
@@ -3911,37 +3911,37 @@
         <v>0.509</v>
       </c>
       <c r="M32">
-        <v>2.447604</v>
+        <v>2.5291908</v>
       </c>
       <c r="N32">
-        <v>-1.938604</v>
+        <v>-2.0201908</v>
       </c>
       <c r="O32">
-        <v>-0.36833476</v>
+        <v>-0.3838362520000001</v>
       </c>
       <c r="P32">
-        <v>-1.57026924</v>
+        <v>-1.636354548</v>
       </c>
       <c r="Q32">
-        <v>-1.32226924</v>
+        <v>-1.388354548</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1361710750024605</v>
+        <v>0.1374808007271338</v>
       </c>
       <c r="T32">
-        <v>1.655177975680705</v>
+        <v>1.679166062284773</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03951211061920147</v>
+        <v>0.03823752640567884</v>
       </c>
       <c r="W32">
-        <v>0.2264830443159923</v>
+        <v>0.2267835912735409</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2079584769431656</v>
+        <v>0.201250138977257</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.16516466579652</v>
+        <v>0.16706466579652</v>
       </c>
       <c r="C33">
-        <v>8.354896222956716</v>
+        <v>7.727637848148278</v>
       </c>
       <c r="D33">
-        <v>17.95089622295672</v>
+        <v>17.66963784814828</v>
       </c>
       <c r="E33">
-        <v>10.726</v>
+        <v>11.072</v>
       </c>
       <c r="F33">
-        <v>10.726</v>
+        <v>11.072</v>
       </c>
       <c r="G33">
         <v>1.13</v>
@@ -3993,37 +3993,37 @@
         <v>0.509</v>
       </c>
       <c r="M33">
-        <v>2.5291908</v>
+        <v>2.6107776</v>
       </c>
       <c r="N33">
-        <v>-2.0201908</v>
+        <v>-2.101777600000001</v>
       </c>
       <c r="O33">
-        <v>-0.3838362520000001</v>
+        <v>-0.3993377440000001</v>
       </c>
       <c r="P33">
-        <v>-1.636354548</v>
+        <v>-1.702439856</v>
       </c>
       <c r="Q33">
-        <v>-1.388354548</v>
+        <v>-1.454439856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1374808007271338</v>
+        <v>0.1388290477966505</v>
       </c>
       <c r="T33">
-        <v>1.679166062284773</v>
+        <v>1.703859680847784</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03823752640567884</v>
+        <v>0.03704260370550137</v>
       </c>
       <c r="W33">
-        <v>0.2267835912735409</v>
+        <v>0.2270653540462428</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.201250138977257</v>
+        <v>0.1949610721342178</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.16706466579652</v>
+        <v>0.16896466579652</v>
       </c>
       <c r="C34">
-        <v>7.727637848148278</v>
+        <v>7.109057139270726</v>
       </c>
       <c r="D34">
-        <v>17.66963784814828</v>
+        <v>17.39705713927073</v>
       </c>
       <c r="E34">
-        <v>11.072</v>
+        <v>11.418</v>
       </c>
       <c r="F34">
-        <v>11.072</v>
+        <v>11.418</v>
       </c>
       <c r="G34">
         <v>1.13</v>
@@ -4075,37 +4075,37 @@
         <v>0.509</v>
       </c>
       <c r="M34">
-        <v>2.6107776</v>
+        <v>2.6923644</v>
       </c>
       <c r="N34">
-        <v>-2.101777600000001</v>
+        <v>-2.1833644</v>
       </c>
       <c r="O34">
-        <v>-0.3993377440000001</v>
+        <v>-0.4148392360000001</v>
       </c>
       <c r="P34">
-        <v>-1.702439856</v>
+        <v>-1.768525164</v>
       </c>
       <c r="Q34">
-        <v>-1.454439856</v>
+        <v>-1.520525164</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1388290477966505</v>
+        <v>0.1402175410473467</v>
       </c>
       <c r="T34">
-        <v>1.703859680847784</v>
+        <v>1.729290422352975</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03704260370550137</v>
+        <v>0.03592010056291043</v>
       </c>
       <c r="W34">
-        <v>0.2270653540462428</v>
+        <v>0.2273300402872657</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1949610721342178</v>
+        <v>0.1890531608574233</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.16896466579652</v>
+        <v>0.17086466579652</v>
       </c>
       <c r="C35">
-        <v>7.109057139270726</v>
+        <v>6.49875859935864</v>
       </c>
       <c r="D35">
-        <v>17.39705713927073</v>
+        <v>17.13275859935864</v>
       </c>
       <c r="E35">
-        <v>11.418</v>
+        <v>11.764</v>
       </c>
       <c r="F35">
-        <v>11.418</v>
+        <v>11.764</v>
       </c>
       <c r="G35">
         <v>1.13</v>
@@ -4157,37 +4157,37 @@
         <v>0.509</v>
       </c>
       <c r="M35">
-        <v>2.6923644</v>
+        <v>2.7739512</v>
       </c>
       <c r="N35">
-        <v>-2.1833644</v>
+        <v>-2.2649512</v>
       </c>
       <c r="O35">
-        <v>-0.4148392360000001</v>
+        <v>-0.4303407280000001</v>
       </c>
       <c r="P35">
-        <v>-1.768525164</v>
+        <v>-1.834610472</v>
       </c>
       <c r="Q35">
-        <v>-1.520525164</v>
+        <v>-1.586610472</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1402175410473467</v>
+        <v>0.1416481098510944</v>
       </c>
       <c r="T35">
-        <v>1.729290422352975</v>
+        <v>1.755491792388627</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03592010056291043</v>
+        <v>0.03486362701694248</v>
       </c>
       <c r="W35">
-        <v>0.2273300402872657</v>
+        <v>0.227579156749405</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1890531608574233</v>
+        <v>0.1834927737733814</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.17086466579652</v>
+        <v>0.17276466579652</v>
       </c>
       <c r="C36">
-        <v>6.49875859935864</v>
+        <v>5.896370405568154</v>
       </c>
       <c r="D36">
-        <v>17.13275859935864</v>
+        <v>16.87637040556816</v>
       </c>
       <c r="E36">
-        <v>11.764</v>
+        <v>12.11</v>
       </c>
       <c r="F36">
-        <v>11.764</v>
+        <v>12.11</v>
       </c>
       <c r="G36">
         <v>1.13</v>
@@ -4239,37 +4239,37 @@
         <v>0.509</v>
       </c>
       <c r="M36">
-        <v>2.7739512</v>
+        <v>2.855538000000001</v>
       </c>
       <c r="N36">
-        <v>-2.2649512</v>
+        <v>-2.346538000000001</v>
       </c>
       <c r="O36">
-        <v>-0.4303407280000001</v>
+        <v>-0.4458422200000001</v>
       </c>
       <c r="P36">
-        <v>-1.834610472</v>
+        <v>-1.900695780000001</v>
       </c>
       <c r="Q36">
-        <v>-1.586610472</v>
+        <v>-1.652695780000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1416481098510944</v>
+        <v>0.1431226961564959</v>
       </c>
       <c r="T36">
-        <v>1.755491792388627</v>
+        <v>1.782499358425375</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03486362701694248</v>
+        <v>0.03386752338788697</v>
       </c>
       <c r="W36">
-        <v>0.227579156749405</v>
+        <v>0.2278140379851362</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1834927737733814</v>
+        <v>0.1782501230941419</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.17276466579652</v>
+        <v>0.17466466579652</v>
       </c>
       <c r="C37">
-        <v>5.896370405568154</v>
+        <v>5.301542663903026</v>
       </c>
       <c r="D37">
-        <v>16.87637040556816</v>
+        <v>16.62754266390303</v>
       </c>
       <c r="E37">
-        <v>12.11</v>
+        <v>12.456</v>
       </c>
       <c r="F37">
-        <v>12.11</v>
+        <v>12.456</v>
       </c>
       <c r="G37">
         <v>1.13</v>
@@ -4321,37 +4321,37 @@
         <v>0.509</v>
       </c>
       <c r="M37">
-        <v>2.855538000000001</v>
+        <v>2.9371248</v>
       </c>
       <c r="N37">
-        <v>-2.346538000000001</v>
+        <v>-2.4281248</v>
       </c>
       <c r="O37">
-        <v>-0.4458422200000001</v>
+        <v>-0.4613437120000001</v>
       </c>
       <c r="P37">
-        <v>-1.900695780000001</v>
+        <v>-1.966781088</v>
       </c>
       <c r="Q37">
-        <v>-1.652695780000001</v>
+        <v>-1.718781088</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1431226961564959</v>
+        <v>0.1446433632839411</v>
       </c>
       <c r="T37">
-        <v>1.782499358425375</v>
+        <v>1.810350910900771</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03386752338788697</v>
+        <v>0.03292675884933455</v>
       </c>
       <c r="W37">
-        <v>0.2278140379851362</v>
+        <v>0.2280358702633269</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1782501230941419</v>
+        <v>0.1732987307859714</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.17466466579652</v>
+        <v>0.17656466579652</v>
       </c>
       <c r="C38">
-        <v>5.301542663903028</v>
+        <v>4.713945816092664</v>
       </c>
       <c r="D38">
-        <v>16.62754266390303</v>
+        <v>16.38594581609266</v>
       </c>
       <c r="E38">
-        <v>12.456</v>
+        <v>12.802</v>
       </c>
       <c r="F38">
-        <v>12.456</v>
+        <v>12.802</v>
       </c>
       <c r="G38">
         <v>1.13</v>
@@ -4403,37 +4403,37 @@
         <v>0.509</v>
       </c>
       <c r="M38">
-        <v>2.9371248</v>
+        <v>3.0187116</v>
       </c>
       <c r="N38">
-        <v>-2.4281248</v>
+        <v>-2.5097116</v>
       </c>
       <c r="O38">
-        <v>-0.461343712</v>
+        <v>-0.476845204</v>
       </c>
       <c r="P38">
-        <v>-1.966781088</v>
+        <v>-2.032866396</v>
       </c>
       <c r="Q38">
-        <v>-1.718781088</v>
+        <v>-1.784866396</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1446433632839411</v>
+        <v>0.1462123055582893</v>
       </c>
       <c r="T38">
-        <v>1.810350910900771</v>
+        <v>1.839086639645227</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03292675884933456</v>
+        <v>0.03203684644800119</v>
       </c>
       <c r="W38">
-        <v>0.2280358702633269</v>
+        <v>0.2282457116075613</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1732987307859714</v>
+        <v>0.1686149813052694</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.17656466579652</v>
+        <v>0.17846466579652</v>
       </c>
       <c r="C39">
-        <v>4.713945816092664</v>
+        <v>4.133269183368705</v>
       </c>
       <c r="D39">
-        <v>16.38594581609266</v>
+        <v>16.15126918336871</v>
       </c>
       <c r="E39">
-        <v>12.802</v>
+        <v>13.148</v>
       </c>
       <c r="F39">
-        <v>12.802</v>
+        <v>13.148</v>
       </c>
       <c r="G39">
         <v>1.13</v>
@@ -4485,37 +4485,37 @@
         <v>0.509</v>
       </c>
       <c r="M39">
-        <v>3.0187116</v>
+        <v>3.100298400000001</v>
       </c>
       <c r="N39">
-        <v>-2.5097116</v>
+        <v>-2.591298400000001</v>
       </c>
       <c r="O39">
-        <v>-0.476845204</v>
+        <v>-0.4923466960000001</v>
       </c>
       <c r="P39">
-        <v>-2.032866396</v>
+        <v>-2.098951704000001</v>
       </c>
       <c r="Q39">
-        <v>-1.784866396</v>
+        <v>-1.850951704000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1462123055582893</v>
+        <v>0.1478318588737456</v>
       </c>
       <c r="T39">
-        <v>1.839086639645227</v>
+        <v>1.868749327381441</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03203684644800119</v>
+        <v>0.03119377154147484</v>
       </c>
       <c r="W39">
-        <v>0.2282457116075613</v>
+        <v>0.2284445086705202</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1686149813052694</v>
+        <v>0.1641777449551307</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.17846466579652</v>
+        <v>0.18036466579652</v>
       </c>
       <c r="C40">
-        <v>4.133269183368705</v>
+        <v>3.559219633609453</v>
       </c>
       <c r="D40">
-        <v>16.15126918336871</v>
+        <v>15.92321963360945</v>
       </c>
       <c r="E40">
-        <v>13.148</v>
+        <v>13.494</v>
       </c>
       <c r="F40">
-        <v>13.148</v>
+        <v>13.494</v>
       </c>
       <c r="G40">
         <v>1.13</v>
@@ -4567,37 +4567,37 @@
         <v>0.509</v>
       </c>
       <c r="M40">
-        <v>3.100298400000001</v>
+        <v>3.1818852</v>
       </c>
       <c r="N40">
-        <v>-2.591298400000001</v>
+        <v>-2.672885200000001</v>
       </c>
       <c r="O40">
-        <v>-0.4923466960000001</v>
+        <v>-0.5078481880000001</v>
       </c>
       <c r="P40">
-        <v>-2.098951704000001</v>
+        <v>-2.165037012</v>
       </c>
       <c r="Q40">
-        <v>-1.850951704000001</v>
+        <v>-1.917037012</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1478318588737456</v>
+        <v>0.1495045122979054</v>
       </c>
       <c r="T40">
-        <v>1.868749327381441</v>
+        <v>1.899384562256547</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03119377154147484</v>
+        <v>0.03039393124553959</v>
       </c>
       <c r="W40">
-        <v>0.2284445086705202</v>
+        <v>0.2286331110123018</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1641777449551307</v>
+        <v>0.1599680591870505</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.18036466579652</v>
+        <v>0.18226466579652</v>
       </c>
       <c r="C41">
-        <v>3.559219633609453</v>
+        <v>2.991520359828433</v>
       </c>
       <c r="D41">
-        <v>15.92321963360945</v>
+        <v>15.70152035982843</v>
       </c>
       <c r="E41">
-        <v>13.494</v>
+        <v>13.84</v>
       </c>
       <c r="F41">
-        <v>13.494</v>
+        <v>13.84</v>
       </c>
       <c r="G41">
         <v>1.13</v>
@@ -4649,37 +4649,37 @@
         <v>0.509</v>
       </c>
       <c r="M41">
-        <v>3.1818852</v>
+        <v>3.263472000000001</v>
       </c>
       <c r="N41">
-        <v>-2.672885200000001</v>
+        <v>-2.754472000000001</v>
       </c>
       <c r="O41">
-        <v>-0.5078481880000001</v>
+        <v>-0.5233496800000002</v>
       </c>
       <c r="P41">
-        <v>-2.165037012</v>
+        <v>-2.231122320000001</v>
       </c>
       <c r="Q41">
-        <v>-1.917037012</v>
+        <v>-1.983122320000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1495045122979054</v>
+        <v>0.1512329208362038</v>
       </c>
       <c r="T41">
-        <v>1.899384562256547</v>
+        <v>1.931040971627489</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03039393124553959</v>
+        <v>0.0296340829644011</v>
       </c>
       <c r="W41">
-        <v>0.2286331110123018</v>
+        <v>0.2288122832369942</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1599680591870505</v>
+        <v>0.1559688577073741</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.18226466579652</v>
+        <v>0.18416466579652</v>
       </c>
       <c r="C42">
-        <v>2.991520359828433</v>
+        <v>2.429909759304548</v>
       </c>
       <c r="D42">
-        <v>15.70152035982843</v>
+        <v>15.48590975930455</v>
       </c>
       <c r="E42">
-        <v>13.84</v>
+        <v>14.186</v>
       </c>
       <c r="F42">
-        <v>13.84</v>
+        <v>14.186</v>
       </c>
       <c r="G42">
         <v>1.13</v>
@@ -4731,37 +4731,37 @@
         <v>0.509</v>
       </c>
       <c r="M42">
-        <v>3.263472000000001</v>
+        <v>3.3450588</v>
       </c>
       <c r="N42">
-        <v>-2.754472000000001</v>
+        <v>-2.8360588</v>
       </c>
       <c r="O42">
-        <v>-0.5233496800000002</v>
+        <v>-0.5388511720000001</v>
       </c>
       <c r="P42">
-        <v>-2.231122320000001</v>
+        <v>-2.297207628</v>
       </c>
       <c r="Q42">
-        <v>-1.983122320000001</v>
+        <v>-2.049207628</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1512329208362038</v>
+        <v>0.1530199194944446</v>
       </c>
       <c r="T42">
-        <v>1.931040971627489</v>
+        <v>1.963770479621175</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0296340829644011</v>
+        <v>0.02891130045307425</v>
       </c>
       <c r="W42">
-        <v>0.2288122832369942</v>
+        <v>0.2289827153531651</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1559688577073741</v>
+        <v>0.1521647392267065</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.18416466579652</v>
+        <v>0.18606466579652</v>
       </c>
       <c r="C43">
-        <v>2.429909759304548</v>
+        <v>1.874140403810825</v>
       </c>
       <c r="D43">
-        <v>15.48590975930455</v>
+        <v>15.27614040381083</v>
       </c>
       <c r="E43">
-        <v>14.186</v>
+        <v>14.532</v>
       </c>
       <c r="F43">
-        <v>14.186</v>
+        <v>14.532</v>
       </c>
       <c r="G43">
         <v>1.13</v>
@@ -4813,37 +4813,37 @@
         <v>0.509</v>
       </c>
       <c r="M43">
-        <v>3.3450588</v>
+        <v>3.426645600000001</v>
       </c>
       <c r="N43">
-        <v>-2.8360588</v>
+        <v>-2.917645600000001</v>
       </c>
       <c r="O43">
-        <v>-0.5388511720000001</v>
+        <v>-0.5543526640000002</v>
       </c>
       <c r="P43">
-        <v>-2.297207628</v>
+        <v>-2.363292936000001</v>
       </c>
       <c r="Q43">
-        <v>-2.049207628</v>
+        <v>-2.115292936</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1530199194944446</v>
+        <v>0.154868538796073</v>
       </c>
       <c r="T43">
-        <v>1.963770479621175</v>
+        <v>1.997628591338782</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02891130045307425</v>
+        <v>0.02822293615657248</v>
       </c>
       <c r="W43">
-        <v>0.2289827153531651</v>
+        <v>0.2291450316542802</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1521647392267065</v>
+        <v>0.1485417692451183</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.18606466579652</v>
+        <v>0.18796466579652</v>
       </c>
       <c r="C44">
-        <v>1.874140403810831</v>
+        <v>1.323978092419164</v>
       </c>
       <c r="D44">
-        <v>15.27614040381083</v>
+        <v>15.07197809241917</v>
       </c>
       <c r="E44">
-        <v>14.532</v>
+        <v>14.878</v>
       </c>
       <c r="F44">
-        <v>14.532</v>
+        <v>14.878</v>
       </c>
       <c r="G44">
         <v>1.13</v>
@@ -4895,37 +4895,37 @@
         <v>0.509</v>
       </c>
       <c r="M44">
-        <v>3.4266456</v>
+        <v>3.5082324</v>
       </c>
       <c r="N44">
-        <v>-2.9176456</v>
+        <v>-2.9992324</v>
       </c>
       <c r="O44">
-        <v>-0.5543526640000001</v>
+        <v>-0.5698541560000001</v>
       </c>
       <c r="P44">
-        <v>-2.363292936</v>
+        <v>-2.429378244</v>
       </c>
       <c r="Q44">
-        <v>-2.115292936</v>
+        <v>-2.181378244</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1548685387960729</v>
+        <v>0.1567820219328462</v>
       </c>
       <c r="T44">
-        <v>1.997628591338781</v>
+        <v>2.032674706976304</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02822293615657248</v>
+        <v>0.02756658880409405</v>
       </c>
       <c r="W44">
-        <v>0.2291450316542802</v>
+        <v>0.2292997983599946</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1485417692451183</v>
+        <v>0.1450873094952319</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.18796466579652</v>
+        <v>0.18986466579652</v>
       </c>
       <c r="C45">
-        <v>1.323978092419164</v>
+        <v>0.7792009792577517</v>
       </c>
       <c r="D45">
-        <v>15.07197809241917</v>
+        <v>14.87320097925775</v>
       </c>
       <c r="E45">
-        <v>14.878</v>
+        <v>15.224</v>
       </c>
       <c r="F45">
-        <v>14.878</v>
+        <v>15.224</v>
       </c>
       <c r="G45">
         <v>1.13</v>
@@ -4977,37 +4977,37 @@
         <v>0.509</v>
       </c>
       <c r="M45">
-        <v>3.5082324</v>
+        <v>3.5898192</v>
       </c>
       <c r="N45">
-        <v>-2.9992324</v>
+        <v>-3.0808192</v>
       </c>
       <c r="O45">
-        <v>-0.5698541560000001</v>
+        <v>-0.5853556480000001</v>
       </c>
       <c r="P45">
-        <v>-2.429378244</v>
+        <v>-2.495463552</v>
       </c>
       <c r="Q45">
-        <v>-2.181378244</v>
+        <v>-2.247463552</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1567820219328462</v>
+        <v>0.1587638437530755</v>
       </c>
       <c r="T45">
-        <v>2.032674706976304</v>
+        <v>2.068972469600881</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02756658880409405</v>
+        <v>0.02694007542218282</v>
       </c>
       <c r="W45">
-        <v>0.2292997983599946</v>
+        <v>0.2294475302154493</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1450873094952319</v>
+        <v>0.1417898706430675</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.18986466579652</v>
+        <v>0.19176466579652</v>
       </c>
       <c r="C46">
-        <v>0.7792009792577517</v>
+        <v>0.239598769391538</v>
       </c>
       <c r="D46">
-        <v>14.87320097925775</v>
+        <v>14.67959876939154</v>
       </c>
       <c r="E46">
-        <v>15.224</v>
+        <v>15.57</v>
       </c>
       <c r="F46">
-        <v>15.224</v>
+        <v>15.57</v>
       </c>
       <c r="G46">
         <v>1.13</v>
@@ -5059,37 +5059,37 @@
         <v>0.509</v>
       </c>
       <c r="M46">
-        <v>3.5898192</v>
+        <v>3.671406</v>
       </c>
       <c r="N46">
-        <v>-3.0808192</v>
+        <v>-3.162406</v>
       </c>
       <c r="O46">
-        <v>-0.5853556480000001</v>
+        <v>-0.60085714</v>
       </c>
       <c r="P46">
-        <v>-2.495463552</v>
+        <v>-2.56154886</v>
       </c>
       <c r="Q46">
-        <v>-2.247463552</v>
+        <v>-2.31354886</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1587638437530755</v>
+        <v>0.1608177318213133</v>
       </c>
       <c r="T46">
-        <v>2.068972469600881</v>
+        <v>2.106590150866351</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02694007542218282</v>
+        <v>0.02634140707946764</v>
       </c>
       <c r="W46">
-        <v>0.2294475302154493</v>
+        <v>0.2295886962106616</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1417898706430675</v>
+        <v>0.1386389846287771</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.19176466579652</v>
+        <v>0.19366466579652</v>
       </c>
       <c r="C47">
-        <v>0.239598769391538</v>
+        <v>-0.2950280233016276</v>
       </c>
       <c r="D47">
-        <v>14.67959876939154</v>
+        <v>14.49097197669837</v>
       </c>
       <c r="E47">
-        <v>15.57</v>
+        <v>15.916</v>
       </c>
       <c r="F47">
-        <v>15.57</v>
+        <v>15.916</v>
       </c>
       <c r="G47">
         <v>1.13</v>
@@ -5141,37 +5141,37 @@
         <v>0.509</v>
       </c>
       <c r="M47">
-        <v>3.671406</v>
+        <v>3.752992800000001</v>
       </c>
       <c r="N47">
-        <v>-3.162406</v>
+        <v>-3.243992800000001</v>
       </c>
       <c r="O47">
-        <v>-0.60085714</v>
+        <v>-0.6163586320000002</v>
       </c>
       <c r="P47">
-        <v>-2.56154886</v>
+        <v>-2.627634168000001</v>
       </c>
       <c r="Q47">
-        <v>-2.31354886</v>
+        <v>-2.379634168000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1608177318213133</v>
+        <v>0.1629476898180043</v>
       </c>
       <c r="T47">
-        <v>2.106590150866351</v>
+        <v>2.145601079586099</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02634140707946764</v>
+        <v>0.02576876779513139</v>
       </c>
       <c r="W47">
-        <v>0.2295886962106616</v>
+        <v>0.229723724553908</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1386389846287771</v>
+        <v>0.1356250936585862</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.19366466579652</v>
+        <v>0.19556466579652</v>
       </c>
       <c r="C48">
-        <v>-0.2950280233016276</v>
+        <v>-0.8248687617648294</v>
       </c>
       <c r="D48">
-        <v>14.49097197669837</v>
+        <v>14.30713123823517</v>
       </c>
       <c r="E48">
-        <v>15.916</v>
+        <v>16.262</v>
       </c>
       <c r="F48">
-        <v>15.916</v>
+        <v>16.262</v>
       </c>
       <c r="G48">
         <v>1.13</v>
@@ -5223,37 +5223,37 @@
         <v>0.509</v>
       </c>
       <c r="M48">
-        <v>3.752992800000001</v>
+        <v>3.8345796</v>
       </c>
       <c r="N48">
-        <v>-3.243992800000001</v>
+        <v>-3.3255796</v>
       </c>
       <c r="O48">
-        <v>-0.6163586320000002</v>
+        <v>-0.631860124</v>
       </c>
       <c r="P48">
-        <v>-2.627634168000001</v>
+        <v>-2.693719476</v>
       </c>
       <c r="Q48">
-        <v>-2.379634168000001</v>
+        <v>-2.445719476</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1629476898180043</v>
+        <v>0.1651580235881553</v>
       </c>
       <c r="T48">
-        <v>2.145601079586099</v>
+        <v>2.186084118823572</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02576876779513139</v>
+        <v>0.02522049613991583</v>
       </c>
       <c r="W48">
-        <v>0.229723724553908</v>
+        <v>0.2298530070102079</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1356250936585862</v>
+        <v>0.132739453367978</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.19556466579652</v>
+        <v>0.19746466579652</v>
       </c>
       <c r="C49">
-        <v>-0.8248687617648294</v>
+        <v>-1.350103319859706</v>
       </c>
       <c r="D49">
-        <v>14.30713123823517</v>
+        <v>14.12789668014029</v>
       </c>
       <c r="E49">
-        <v>16.262</v>
+        <v>16.608</v>
       </c>
       <c r="F49">
-        <v>16.262</v>
+        <v>16.608</v>
       </c>
       <c r="G49">
         <v>1.13</v>
@@ -5305,37 +5305,37 @@
         <v>0.509</v>
       </c>
       <c r="M49">
-        <v>3.8345796</v>
+        <v>3.9161664</v>
       </c>
       <c r="N49">
-        <v>-3.3255796</v>
+        <v>-3.4071664</v>
       </c>
       <c r="O49">
-        <v>-0.631860124</v>
+        <v>-0.6473616160000001</v>
       </c>
       <c r="P49">
-        <v>-2.693719476</v>
+        <v>-2.759804784</v>
       </c>
       <c r="Q49">
-        <v>-2.445719476</v>
+        <v>-2.511804784000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1651580235881553</v>
+        <v>0.1674533701956198</v>
       </c>
       <c r="T49">
-        <v>2.186084118823572</v>
+        <v>2.228124198031718</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02522049613991583</v>
+        <v>0.02469506913700092</v>
       </c>
       <c r="W49">
-        <v>0.2298530070102079</v>
+        <v>0.2299769026974952</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.132739453367978</v>
+        <v>0.1299740480894785</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.19746466579652</v>
+        <v>0.19936466579652</v>
       </c>
       <c r="C50">
-        <v>-1.350103319859706</v>
+        <v>-1.870902669391292</v>
       </c>
       <c r="D50">
-        <v>14.12789668014029</v>
+        <v>13.95309733060871</v>
       </c>
       <c r="E50">
-        <v>16.608</v>
+        <v>16.954</v>
       </c>
       <c r="F50">
-        <v>16.608</v>
+        <v>16.954</v>
       </c>
       <c r="G50">
         <v>1.13</v>
@@ -5387,37 +5387,37 @@
         <v>0.509</v>
       </c>
       <c r="M50">
-        <v>3.9161664</v>
+        <v>3.9977532</v>
       </c>
       <c r="N50">
-        <v>-3.4071664</v>
+        <v>-3.488753200000001</v>
       </c>
       <c r="O50">
-        <v>-0.6473616160000001</v>
+        <v>-0.6628631080000001</v>
       </c>
       <c r="P50">
-        <v>-2.759804784</v>
+        <v>-2.825890092</v>
       </c>
       <c r="Q50">
-        <v>-2.511804784000001</v>
+        <v>-2.577890092000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1674533701956198</v>
+        <v>0.1698387303955339</v>
       </c>
       <c r="T50">
-        <v>2.228124198031718</v>
+        <v>2.271812907797046</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02469506913700092</v>
+        <v>0.02419108813420498</v>
       </c>
       <c r="W50">
-        <v>0.2299769026974952</v>
+        <v>0.2300957414179545</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1299740480894785</v>
+        <v>0.1273215164958157</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.19936466579652</v>
+        <v>0.20126466579652</v>
       </c>
       <c r="C51">
-        <v>-1.870902669391292</v>
+        <v>-2.387429424087149</v>
       </c>
       <c r="D51">
-        <v>13.95309733060871</v>
+        <v>13.78257057591285</v>
       </c>
       <c r="E51">
-        <v>16.954</v>
+        <v>17.3</v>
       </c>
       <c r="F51">
-        <v>16.954</v>
+        <v>17.3</v>
       </c>
       <c r="G51">
         <v>1.13</v>
@@ -5469,37 +5469,37 @@
         <v>0.509</v>
       </c>
       <c r="M51">
-        <v>3.9977532</v>
+        <v>4.07934</v>
       </c>
       <c r="N51">
-        <v>-3.488753200000001</v>
+        <v>-3.57034</v>
       </c>
       <c r="O51">
-        <v>-0.6628631080000001</v>
+        <v>-0.6783646000000001</v>
       </c>
       <c r="P51">
-        <v>-2.825890092</v>
+        <v>-2.8919754</v>
       </c>
       <c r="Q51">
-        <v>-2.577890092000001</v>
+        <v>-2.6439754</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1698387303955339</v>
+        <v>0.1723195050034446</v>
       </c>
       <c r="T51">
-        <v>2.271812907797046</v>
+        <v>2.317249165952987</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02419108813420498</v>
+        <v>0.02370726637152088</v>
       </c>
       <c r="W51">
-        <v>0.2300957414179545</v>
+        <v>0.2302098265895954</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1273215164958157</v>
+        <v>0.1247750861658994</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.20126466579652</v>
+        <v>0.20316466579652</v>
       </c>
       <c r="C52">
-        <v>-2.387429424087149</v>
+        <v>-2.899838344168959</v>
       </c>
       <c r="D52">
-        <v>13.78257057591285</v>
+        <v>13.61616165583104</v>
       </c>
       <c r="E52">
-        <v>17.3</v>
+        <v>17.646</v>
       </c>
       <c r="F52">
-        <v>17.3</v>
+        <v>17.646</v>
       </c>
       <c r="G52">
         <v>1.13</v>
@@ -5551,37 +5551,37 @@
         <v>0.509</v>
       </c>
       <c r="M52">
-        <v>4.07934</v>
+        <v>4.1609268</v>
       </c>
       <c r="N52">
-        <v>-3.57034</v>
+        <v>-3.6519268</v>
       </c>
       <c r="O52">
-        <v>-0.6783646000000001</v>
+        <v>-0.693866092</v>
       </c>
       <c r="P52">
-        <v>-2.8919754</v>
+        <v>-2.958060708000001</v>
       </c>
       <c r="Q52">
-        <v>-2.6439754</v>
+        <v>-2.710060708</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1723195050034446</v>
+        <v>0.1749015357178006</v>
       </c>
       <c r="T52">
-        <v>2.317249165952987</v>
+        <v>2.364539965258149</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02370726637152088</v>
+        <v>0.02324241801129498</v>
       </c>
       <c r="W52">
-        <v>0.2302098265895954</v>
+        <v>0.2303194378329367</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1247750861658994</v>
+        <v>0.1223285158489209</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.20316466579652</v>
+        <v>0.20506466579652</v>
       </c>
       <c r="C53">
-        <v>-2.899838344168959</v>
+        <v>-3.408276804807379</v>
       </c>
       <c r="D53">
-        <v>13.61616165583104</v>
+        <v>13.45372319519262</v>
       </c>
       <c r="E53">
-        <v>17.646</v>
+        <v>17.992</v>
       </c>
       <c r="F53">
-        <v>17.646</v>
+        <v>17.992</v>
       </c>
       <c r="G53">
         <v>1.13</v>
@@ -5633,37 +5633,37 @@
         <v>0.509</v>
       </c>
       <c r="M53">
-        <v>4.1609268</v>
+        <v>4.242513600000001</v>
       </c>
       <c r="N53">
-        <v>-3.6519268</v>
+        <v>-3.733513600000001</v>
       </c>
       <c r="O53">
-        <v>-0.693866092</v>
+        <v>-0.7093675840000001</v>
       </c>
       <c r="P53">
-        <v>-2.958060708000001</v>
+        <v>-3.024146016</v>
       </c>
       <c r="Q53">
-        <v>-2.710060708</v>
+        <v>-2.776146016</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1749015357178006</v>
+        <v>0.1775911510452548</v>
       </c>
       <c r="T53">
-        <v>2.364539965258149</v>
+        <v>2.413801214534361</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02324241801129498</v>
+        <v>0.02279544843415469</v>
       </c>
       <c r="W53">
-        <v>0.2303194378329367</v>
+        <v>0.2304248332592263</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1223285158489209</v>
+        <v>0.1199760443902879</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.20506466579652</v>
+        <v>0.20696466579652</v>
       </c>
       <c r="C54">
-        <v>-3.408276804807379</v>
+        <v>-3.912885231440672</v>
       </c>
       <c r="D54">
-        <v>13.45372319519262</v>
+        <v>13.29511476855933</v>
       </c>
       <c r="E54">
-        <v>17.992</v>
+        <v>18.338</v>
       </c>
       <c r="F54">
-        <v>17.992</v>
+        <v>18.338</v>
       </c>
       <c r="G54">
         <v>1.13</v>
@@ -5715,37 +5715,37 @@
         <v>0.509</v>
       </c>
       <c r="M54">
-        <v>4.242513600000001</v>
+        <v>4.324100400000001</v>
       </c>
       <c r="N54">
-        <v>-3.733513600000001</v>
+        <v>-3.815100400000001</v>
       </c>
       <c r="O54">
-        <v>-0.7093675840000001</v>
+        <v>-0.7248690760000002</v>
       </c>
       <c r="P54">
-        <v>-3.024146016</v>
+        <v>-3.090231324000001</v>
       </c>
       <c r="Q54">
-        <v>-2.776146016</v>
+        <v>-2.842231324000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1775911510452548</v>
+        <v>0.1803952180887709</v>
       </c>
       <c r="T54">
-        <v>2.413801214534361</v>
+        <v>2.465158687184029</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02279544843415469</v>
+        <v>0.02236534563351026</v>
       </c>
       <c r="W54">
-        <v>0.2304248332592263</v>
+        <v>0.2305262514996183</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1199760443902879</v>
+        <v>0.1177123454395277</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.20696466579652</v>
+        <v>0.20886466579652</v>
       </c>
       <c r="C55">
-        <v>-3.912885231440672</v>
+        <v>-4.41379750465984</v>
       </c>
       <c r="D55">
-        <v>13.29511476855933</v>
+        <v>13.14020249534016</v>
       </c>
       <c r="E55">
-        <v>18.338</v>
+        <v>18.684</v>
       </c>
       <c r="F55">
-        <v>18.338</v>
+        <v>18.684</v>
       </c>
       <c r="G55">
         <v>1.13</v>
@@ -5797,37 +5797,37 @@
         <v>0.509</v>
       </c>
       <c r="M55">
-        <v>4.324100400000001</v>
+        <v>4.4056872</v>
       </c>
       <c r="N55">
-        <v>-3.815100400000001</v>
+        <v>-3.8966872</v>
       </c>
       <c r="O55">
-        <v>-0.7248690760000002</v>
+        <v>-0.740370568</v>
       </c>
       <c r="P55">
-        <v>-3.090231324000001</v>
+        <v>-3.156316632</v>
       </c>
       <c r="Q55">
-        <v>-2.842231324000001</v>
+        <v>-2.908316632</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1803952180887709</v>
+        <v>0.1833212010907007</v>
       </c>
       <c r="T55">
-        <v>2.465158687184029</v>
+        <v>2.518749093427159</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02236534563351026</v>
+        <v>0.02195117256622304</v>
       </c>
       <c r="W55">
-        <v>0.2305262514996183</v>
+        <v>0.2306239135088846</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1177123454395277</v>
+        <v>0.1155324871906476</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.20886466579652</v>
+        <v>0.21076466579652</v>
       </c>
       <c r="C56">
-        <v>-4.41379750465984</v>
+        <v>-4.911141337113886</v>
       </c>
       <c r="D56">
-        <v>13.14020249534016</v>
+        <v>12.98885866288611</v>
       </c>
       <c r="E56">
-        <v>18.684</v>
+        <v>19.03</v>
       </c>
       <c r="F56">
-        <v>18.684</v>
+        <v>19.03</v>
       </c>
       <c r="G56">
         <v>1.13</v>
@@ -5879,37 +5879,37 @@
         <v>0.509</v>
       </c>
       <c r="M56">
-        <v>4.4056872</v>
+        <v>4.487274</v>
       </c>
       <c r="N56">
-        <v>-3.8966872</v>
+        <v>-3.978274</v>
       </c>
       <c r="O56">
-        <v>-0.740370568</v>
+        <v>-0.7558720600000001</v>
       </c>
       <c r="P56">
-        <v>-3.156316632</v>
+        <v>-3.22240194</v>
       </c>
       <c r="Q56">
-        <v>-2.908316632</v>
+        <v>-2.97440194</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1833212010907007</v>
+        <v>0.1863772277816051</v>
       </c>
       <c r="T56">
-        <v>2.518749093427159</v>
+        <v>2.574721295503319</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02195117256622304</v>
+        <v>0.02155206033774626</v>
       </c>
       <c r="W56">
-        <v>0.2306239135088846</v>
+        <v>0.2307180241723595</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1155324871906476</v>
+        <v>0.113431896514454</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.21076466579652</v>
+        <v>0.21266466579652</v>
       </c>
       <c r="C57">
-        <v>-4.911141337113886</v>
+        <v>-5.40503862466533</v>
       </c>
       <c r="D57">
-        <v>12.98885866288611</v>
+        <v>12.84096137533467</v>
       </c>
       <c r="E57">
-        <v>19.03</v>
+        <v>19.376</v>
       </c>
       <c r="F57">
-        <v>19.03</v>
+        <v>19.376</v>
       </c>
       <c r="G57">
         <v>1.13</v>
@@ -5961,37 +5961,37 @@
         <v>0.509</v>
       </c>
       <c r="M57">
-        <v>4.487274</v>
+        <v>4.5688608</v>
       </c>
       <c r="N57">
-        <v>-3.978274</v>
+        <v>-4.0598608</v>
       </c>
       <c r="O57">
-        <v>-0.7558720600000001</v>
+        <v>-0.771373552</v>
       </c>
       <c r="P57">
-        <v>-3.22240194</v>
+        <v>-3.288487248</v>
       </c>
       <c r="Q57">
-        <v>-2.97440194</v>
+        <v>-3.040487248</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1863772277816051</v>
+        <v>0.1895721647766416</v>
       </c>
       <c r="T57">
-        <v>2.574721295503319</v>
+        <v>2.633237688582939</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02155206033774626</v>
+        <v>0.02116720211742936</v>
       </c>
       <c r="W57">
-        <v>0.2307180241723595</v>
+        <v>0.2308087737407102</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.113431896514454</v>
+        <v>0.1114063269338388</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.21266466579652</v>
+        <v>0.21456466579652</v>
       </c>
       <c r="C58">
-        <v>-5.40503862466533</v>
+        <v>-5.895605773825288</v>
       </c>
       <c r="D58">
-        <v>12.84096137533467</v>
+        <v>12.69639422617471</v>
       </c>
       <c r="E58">
-        <v>19.376</v>
+        <v>19.722</v>
       </c>
       <c r="F58">
-        <v>19.376</v>
+        <v>19.722</v>
       </c>
       <c r="G58">
         <v>1.13</v>
@@ -6043,37 +6043,37 @@
         <v>0.509</v>
       </c>
       <c r="M58">
-        <v>4.5688608</v>
+        <v>4.650447600000001</v>
       </c>
       <c r="N58">
-        <v>-4.0598608</v>
+        <v>-4.1414476</v>
       </c>
       <c r="O58">
-        <v>-0.771373552</v>
+        <v>-0.7868750440000001</v>
       </c>
       <c r="P58">
-        <v>-3.288487248</v>
+        <v>-3.354572556</v>
       </c>
       <c r="Q58">
-        <v>-3.040487248</v>
+        <v>-3.106572556</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1895721647766416</v>
+        <v>0.1929157034923775</v>
       </c>
       <c r="T58">
-        <v>2.633237688582939</v>
+        <v>2.694475774363938</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02116720211742936</v>
+        <v>0.02079584769431656</v>
       </c>
       <c r="W58">
-        <v>0.2308087737407102</v>
+        <v>0.2308963391136802</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1114063269338388</v>
+        <v>0.1094518299700873</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.21456466579652</v>
+        <v>0.21646466579652</v>
       </c>
       <c r="C59">
-        <v>-5.895605773825288</v>
+        <v>-6.382954007316656</v>
       </c>
       <c r="D59">
-        <v>12.69639422617471</v>
+        <v>12.55504599268335</v>
       </c>
       <c r="E59">
-        <v>19.722</v>
+        <v>20.068</v>
       </c>
       <c r="F59">
-        <v>19.722</v>
+        <v>20.068</v>
       </c>
       <c r="G59">
         <v>1.13</v>
@@ -6125,37 +6125,37 @@
         <v>0.509</v>
       </c>
       <c r="M59">
-        <v>4.650447600000001</v>
+        <v>4.732034400000002</v>
       </c>
       <c r="N59">
-        <v>-4.1414476</v>
+        <v>-4.223034400000001</v>
       </c>
       <c r="O59">
-        <v>-0.7868750440000001</v>
+        <v>-0.8023765360000003</v>
       </c>
       <c r="P59">
-        <v>-3.354572556</v>
+        <v>-3.420657864000001</v>
       </c>
       <c r="Q59">
-        <v>-3.106572556</v>
+        <v>-3.172657864000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1929157034923775</v>
+        <v>0.1964184583374341</v>
       </c>
       <c r="T59">
-        <v>2.694475774363938</v>
+        <v>2.758629959467842</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02079584769431656</v>
+        <v>0.02043729859613869</v>
       </c>
       <c r="W59">
-        <v>0.2308963391136802</v>
+        <v>0.2309808849910305</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1094518299700873</v>
+        <v>0.1075647294533616</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.21646466579652</v>
+        <v>0.21836466579652</v>
       </c>
       <c r="C60">
-        <v>-6.382954007316648</v>
+        <v>-6.867189649451099</v>
       </c>
       <c r="D60">
-        <v>12.55504599268335</v>
+        <v>12.4168103505489</v>
       </c>
       <c r="E60">
-        <v>20.068</v>
+        <v>20.414</v>
       </c>
       <c r="F60">
-        <v>20.068</v>
+        <v>20.414</v>
       </c>
       <c r="G60">
         <v>1.13</v>
@@ -6207,37 +6207,37 @@
         <v>0.509</v>
       </c>
       <c r="M60">
-        <v>4.7320344</v>
+        <v>4.813621200000001</v>
       </c>
       <c r="N60">
-        <v>-4.2230344</v>
+        <v>-4.304621200000001</v>
       </c>
       <c r="O60">
-        <v>-0.8023765359999999</v>
+        <v>-0.8178780280000001</v>
       </c>
       <c r="P60">
-        <v>-3.420657864</v>
+        <v>-3.486743172000001</v>
       </c>
       <c r="Q60">
-        <v>-3.172657864</v>
+        <v>-3.238743172</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1964184583374341</v>
+        <v>0.2000920792724935</v>
       </c>
       <c r="T60">
-        <v>2.758629959467841</v>
+        <v>2.825913617015837</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02043729859613869</v>
+        <v>0.02009090370467871</v>
       </c>
       <c r="W60">
-        <v>0.2309808849910305</v>
+        <v>0.2310625649064368</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1075647294533616</v>
+        <v>0.1057415984456775</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.21836466579652</v>
+        <v>0.22026466579652</v>
       </c>
       <c r="C61">
-        <v>-6.867189649451099</v>
+        <v>-7.348414392858786</v>
       </c>
       <c r="D61">
-        <v>12.4168103505489</v>
+        <v>12.28158560714122</v>
       </c>
       <c r="E61">
-        <v>20.414</v>
+        <v>20.76</v>
       </c>
       <c r="F61">
-        <v>20.414</v>
+        <v>20.76</v>
       </c>
       <c r="G61">
         <v>1.13</v>
@@ -6289,37 +6289,37 @@
         <v>0.509</v>
       </c>
       <c r="M61">
-        <v>4.813621200000001</v>
+        <v>4.895208</v>
       </c>
       <c r="N61">
-        <v>-4.304621200000001</v>
+        <v>-4.386208</v>
       </c>
       <c r="O61">
-        <v>-0.8178780280000001</v>
+        <v>-0.83337952</v>
       </c>
       <c r="P61">
-        <v>-3.486743172000001</v>
+        <v>-3.55282848</v>
       </c>
       <c r="Q61">
-        <v>-3.238743172</v>
+        <v>-3.304828479999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2000920792724935</v>
+        <v>0.2039493812543058</v>
       </c>
       <c r="T61">
-        <v>2.825913617015837</v>
+        <v>2.896561457441233</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02009090370467871</v>
+        <v>0.01975605530960074</v>
       </c>
       <c r="W61">
-        <v>0.2310625649064368</v>
+        <v>0.2311415221579961</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1057415984456775</v>
+        <v>0.1039792384715829</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.22026466579652</v>
+        <v>0.22216466579652</v>
       </c>
       <c r="C62">
-        <v>-7.348414392858786</v>
+        <v>-7.82672554797696</v>
       </c>
       <c r="D62">
-        <v>12.28158560714122</v>
+        <v>12.14927445202304</v>
       </c>
       <c r="E62">
-        <v>20.76</v>
+        <v>21.106</v>
       </c>
       <c r="F62">
-        <v>20.76</v>
+        <v>21.106</v>
       </c>
       <c r="G62">
         <v>1.13</v>
@@ -6371,37 +6371,37 @@
         <v>0.509</v>
       </c>
       <c r="M62">
-        <v>4.895208</v>
+        <v>4.9767948</v>
       </c>
       <c r="N62">
-        <v>-4.386208</v>
+        <v>-4.4677948</v>
       </c>
       <c r="O62">
-        <v>-0.83337952</v>
+        <v>-0.848881012</v>
       </c>
       <c r="P62">
-        <v>-3.55282848</v>
+        <v>-3.618913788</v>
       </c>
       <c r="Q62">
-        <v>-3.304828479999999</v>
+        <v>-3.370913788</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2039493812543058</v>
+        <v>0.2080044935941598</v>
       </c>
       <c r="T62">
-        <v>2.896561457441233</v>
+        <v>2.97083226404229</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01975605530960074</v>
+        <v>0.01943218555042695</v>
       </c>
       <c r="W62">
-        <v>0.2311415221579961</v>
+        <v>0.2312178906472094</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1039792384715829</v>
+        <v>0.1022746607917209</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.22216466579652</v>
+        <v>0.22406466579652</v>
       </c>
       <c r="C63">
-        <v>-7.82672554797696</v>
+        <v>-8.302216276583788</v>
       </c>
       <c r="D63">
-        <v>12.14927445202304</v>
+        <v>12.01978372341621</v>
       </c>
       <c r="E63">
-        <v>21.106</v>
+        <v>21.452</v>
       </c>
       <c r="F63">
-        <v>21.106</v>
+        <v>21.452</v>
       </c>
       <c r="G63">
         <v>1.13</v>
@@ -6453,37 +6453,37 @@
         <v>0.509</v>
       </c>
       <c r="M63">
-        <v>4.9767948</v>
+        <v>5.058381600000001</v>
       </c>
       <c r="N63">
-        <v>-4.4677948</v>
+        <v>-4.5493816</v>
       </c>
       <c r="O63">
-        <v>-0.848881012</v>
+        <v>-0.8643825040000001</v>
       </c>
       <c r="P63">
-        <v>-3.618913788</v>
+        <v>-3.684999096</v>
       </c>
       <c r="Q63">
-        <v>-3.370913788</v>
+        <v>-3.436999096</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2080044935941598</v>
+        <v>0.2122730328992692</v>
       </c>
       <c r="T63">
-        <v>2.97083226404229</v>
+        <v>3.049012060464456</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01943218555042695</v>
+        <v>0.01911876320283942</v>
       </c>
       <c r="W63">
-        <v>0.2312178906472094</v>
+        <v>0.2312917956367705</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1022746607917209</v>
+        <v>0.1006250694886286</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.22406466579652</v>
+        <v>0.22596466579652</v>
       </c>
       <c r="C64">
-        <v>-8.302216276583788</v>
+        <v>-8.774975810555251</v>
       </c>
       <c r="D64">
-        <v>12.01978372341621</v>
+        <v>11.89302418944475</v>
       </c>
       <c r="E64">
-        <v>21.452</v>
+        <v>21.798</v>
       </c>
       <c r="F64">
-        <v>21.452</v>
+        <v>21.798</v>
       </c>
       <c r="G64">
         <v>1.13</v>
@@ -6535,37 +6535,37 @@
         <v>0.509</v>
       </c>
       <c r="M64">
-        <v>5.058381600000001</v>
+        <v>5.139968400000001</v>
       </c>
       <c r="N64">
-        <v>-4.5493816</v>
+        <v>-4.6309684</v>
       </c>
       <c r="O64">
-        <v>-0.8643825040000001</v>
+        <v>-0.8798839960000001</v>
       </c>
       <c r="P64">
-        <v>-3.684999096</v>
+        <v>-3.751084404</v>
       </c>
       <c r="Q64">
-        <v>-3.436999096</v>
+        <v>-3.503084404</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2122730328992692</v>
+        <v>0.2167723040587089</v>
       </c>
       <c r="T64">
-        <v>3.049012060464456</v>
+        <v>3.13141779182836</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01911876320283942</v>
+        <v>0.01881529077104832</v>
       </c>
       <c r="W64">
-        <v>0.2312917956367705</v>
+        <v>0.2313633544361868</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1006250694886286</v>
+        <v>0.09902784616341231</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.22596466579652</v>
+        <v>0.22786466579652</v>
       </c>
       <c r="C65">
-        <v>-8.774975810555251</v>
+        <v>-9.245089656924538</v>
       </c>
       <c r="D65">
-        <v>11.89302418944475</v>
+        <v>11.76891034307546</v>
       </c>
       <c r="E65">
-        <v>21.798</v>
+        <v>22.144</v>
       </c>
       <c r="F65">
-        <v>21.798</v>
+        <v>22.144</v>
       </c>
       <c r="G65">
         <v>1.13</v>
@@ -6617,37 +6617,37 @@
         <v>0.509</v>
       </c>
       <c r="M65">
-        <v>5.139968400000001</v>
+        <v>5.221555200000001</v>
       </c>
       <c r="N65">
-        <v>-4.6309684</v>
+        <v>-4.712555200000001</v>
       </c>
       <c r="O65">
-        <v>-0.8798839960000001</v>
+        <v>-0.8953854880000002</v>
       </c>
       <c r="P65">
-        <v>-3.751084404</v>
+        <v>-3.817169712000001</v>
       </c>
       <c r="Q65">
-        <v>-3.503084404</v>
+        <v>-3.569169712000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2167723040587089</v>
+        <v>0.2215215347270064</v>
       </c>
       <c r="T65">
-        <v>3.13141779182836</v>
+        <v>3.218401619379148</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01881529077104832</v>
+        <v>0.01852130185275069</v>
       </c>
       <c r="W65">
-        <v>0.2313633544361868</v>
+        <v>0.2314326770231214</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.09902784616341231</v>
+        <v>0.09748053606710894</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.22786466579652</v>
+        <v>0.22976466579652</v>
       </c>
       <c r="C66">
-        <v>-9.245089656924538</v>
+        <v>-9.712639790234245</v>
       </c>
       <c r="D66">
-        <v>11.76891034307546</v>
+        <v>11.64736020976576</v>
       </c>
       <c r="E66">
-        <v>22.144</v>
+        <v>22.49</v>
       </c>
       <c r="F66">
-        <v>22.144</v>
+        <v>22.49</v>
       </c>
       <c r="G66">
         <v>1.13</v>
@@ -6699,37 +6699,37 @@
         <v>0.509</v>
       </c>
       <c r="M66">
-        <v>5.221555200000001</v>
+        <v>5.303142</v>
       </c>
       <c r="N66">
-        <v>-4.712555200000001</v>
+        <v>-4.794142</v>
       </c>
       <c r="O66">
-        <v>-0.8953854880000002</v>
+        <v>-0.91088698</v>
       </c>
       <c r="P66">
-        <v>-3.817169712000001</v>
+        <v>-3.88325502</v>
       </c>
       <c r="Q66">
-        <v>-3.569169712000001</v>
+        <v>-3.63525502</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2215215347270064</v>
+        <v>0.2265421500049209</v>
       </c>
       <c r="T66">
-        <v>3.218401619379148</v>
+        <v>3.31035595136141</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01852130185275069</v>
+        <v>0.01823635874732376</v>
       </c>
       <c r="W66">
-        <v>0.2314326770231214</v>
+        <v>0.2314998666073811</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.09748053606710894</v>
+        <v>0.09598083551223036</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.22976466579652</v>
+        <v>0.23166466579652</v>
       </c>
       <c r="C67">
-        <v>-9.712639790234245</v>
+        <v>-10.17770483309066</v>
       </c>
       <c r="D67">
-        <v>11.64736020976576</v>
+        <v>11.52829516690934</v>
       </c>
       <c r="E67">
-        <v>22.49</v>
+        <v>22.836</v>
       </c>
       <c r="F67">
-        <v>22.49</v>
+        <v>22.836</v>
       </c>
       <c r="G67">
         <v>1.13</v>
@@ -6781,37 +6781,37 @@
         <v>0.509</v>
       </c>
       <c r="M67">
-        <v>5.303142</v>
+        <v>5.3847288</v>
       </c>
       <c r="N67">
-        <v>-4.794142</v>
+        <v>-4.8757288</v>
       </c>
       <c r="O67">
-        <v>-0.91088698</v>
+        <v>-0.9263884720000001</v>
       </c>
       <c r="P67">
-        <v>-3.88325502</v>
+        <v>-3.949340328</v>
       </c>
       <c r="Q67">
-        <v>-3.63525502</v>
+        <v>-3.701340328</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2265421500049209</v>
+        <v>0.2318580955933009</v>
       </c>
       <c r="T67">
-        <v>3.31035595136141</v>
+        <v>3.407719361695569</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01823635874732376</v>
+        <v>0.01796005028145522</v>
       </c>
       <c r="W67">
-        <v>0.2314998666073811</v>
+        <v>0.2315650201436329</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.09598083551223036</v>
+        <v>0.09452658042871176</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.23166466579652</v>
+        <v>0.23356466579652</v>
       </c>
       <c r="C68">
-        <v>-10.17770483309066</v>
+        <v>-10.64036022575578</v>
       </c>
       <c r="D68">
-        <v>11.52829516690934</v>
+        <v>11.41163977424422</v>
       </c>
       <c r="E68">
-        <v>22.836</v>
+        <v>23.182</v>
       </c>
       <c r="F68">
-        <v>22.836</v>
+        <v>23.182</v>
       </c>
       <c r="G68">
         <v>1.13</v>
@@ -6863,37 +6863,37 @@
         <v>0.509</v>
       </c>
       <c r="M68">
-        <v>5.3847288</v>
+        <v>5.466315600000001</v>
       </c>
       <c r="N68">
-        <v>-4.8757288</v>
+        <v>-4.9573156</v>
       </c>
       <c r="O68">
-        <v>-0.9263884720000001</v>
+        <v>-0.941889964</v>
       </c>
       <c r="P68">
-        <v>-3.949340328</v>
+        <v>-4.015425636</v>
       </c>
       <c r="Q68">
-        <v>-3.701340328</v>
+        <v>-3.767425636</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2318580955933009</v>
+        <v>0.2374962197021888</v>
       </c>
       <c r="T68">
-        <v>3.407719361695569</v>
+        <v>3.510983584777253</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01796005028145522</v>
+        <v>0.01769198982949319</v>
       </c>
       <c r="W68">
-        <v>0.2315650201436329</v>
+        <v>0.2316282287982055</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.09452658042871176</v>
+        <v>0.09311573594470113</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.23356466579652</v>
+        <v>0.23546466579652</v>
       </c>
       <c r="C69">
-        <v>-10.64036022575578</v>
+        <v>-11.10067838554589</v>
       </c>
       <c r="D69">
-        <v>11.41163977424422</v>
+        <v>11.29732161445412</v>
       </c>
       <c r="E69">
-        <v>23.182</v>
+        <v>23.528</v>
       </c>
       <c r="F69">
-        <v>23.182</v>
+        <v>23.528</v>
       </c>
       <c r="G69">
         <v>1.13</v>
@@ -6945,37 +6945,37 @@
         <v>0.509</v>
       </c>
       <c r="M69">
-        <v>5.466315600000001</v>
+        <v>5.547902400000001</v>
       </c>
       <c r="N69">
-        <v>-4.9573156</v>
+        <v>-5.0389024</v>
       </c>
       <c r="O69">
-        <v>-0.941889964</v>
+        <v>-0.9573914560000001</v>
       </c>
       <c r="P69">
-        <v>-4.015425636</v>
+        <v>-4.081510944000001</v>
       </c>
       <c r="Q69">
-        <v>-3.767425636</v>
+        <v>-3.833510944</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2374962197021888</v>
+        <v>0.2434867265678823</v>
       </c>
       <c r="T69">
-        <v>3.510983584777253</v>
+        <v>3.620701821801542</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01769198982949319</v>
+        <v>0.01743181350847124</v>
       </c>
       <c r="W69">
-        <v>0.2316282287982055</v>
+        <v>0.2316895783747025</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.09311573594470113</v>
+        <v>0.09174638688669079</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.23546466579652</v>
+        <v>0.23736466579652</v>
       </c>
       <c r="C70">
-        <v>-11.10067838554589</v>
+        <v>-11.55872885674428</v>
       </c>
       <c r="D70">
-        <v>11.29732161445412</v>
+        <v>11.18527114325572</v>
       </c>
       <c r="E70">
-        <v>23.528</v>
+        <v>23.874</v>
       </c>
       <c r="F70">
-        <v>23.528</v>
+        <v>23.874</v>
       </c>
       <c r="G70">
         <v>1.13</v>
@@ -7027,37 +7027,37 @@
         <v>0.509</v>
       </c>
       <c r="M70">
-        <v>5.547902400000001</v>
+        <v>5.629489200000001</v>
       </c>
       <c r="N70">
-        <v>-5.0389024</v>
+        <v>-5.120489200000001</v>
       </c>
       <c r="O70">
-        <v>-0.9573914560000001</v>
+        <v>-0.9728929480000001</v>
       </c>
       <c r="P70">
-        <v>-4.081510944000001</v>
+        <v>-4.147596252</v>
       </c>
       <c r="Q70">
-        <v>-3.833510944</v>
+        <v>-3.899596252</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2434867265678823</v>
+        <v>0.2498637177474914</v>
       </c>
       <c r="T70">
-        <v>3.620701821801542</v>
+        <v>3.737498654762883</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01743181350847124</v>
+        <v>0.0171791785300876</v>
       </c>
       <c r="W70">
-        <v>0.2316895783747025</v>
+        <v>0.2317491497026054</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.09174638688669079</v>
+        <v>0.09041672910572429</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.23736466579652</v>
+        <v>0.23926466579652</v>
       </c>
       <c r="C71">
-        <v>-11.55872885674428</v>
+        <v>-12.01457845168033</v>
       </c>
       <c r="D71">
-        <v>11.18527114325572</v>
+        <v>11.07542154831967</v>
       </c>
       <c r="E71">
-        <v>23.874</v>
+        <v>24.22</v>
       </c>
       <c r="F71">
-        <v>23.874</v>
+        <v>24.22</v>
       </c>
       <c r="G71">
         <v>1.13</v>
@@ -7109,37 +7109,37 @@
         <v>0.509</v>
       </c>
       <c r="M71">
-        <v>5.629489200000001</v>
+        <v>5.711076000000001</v>
       </c>
       <c r="N71">
-        <v>-5.120489200000001</v>
+        <v>-5.202076000000001</v>
       </c>
       <c r="O71">
-        <v>-0.9728929480000001</v>
+        <v>-0.9883944400000002</v>
       </c>
       <c r="P71">
-        <v>-4.147596252</v>
+        <v>-4.21368156</v>
       </c>
       <c r="Q71">
-        <v>-3.899596252</v>
+        <v>-3.96568156</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2498637177474914</v>
+        <v>0.2566658416724077</v>
       </c>
       <c r="T71">
-        <v>3.737498654762883</v>
+        <v>3.862081943254978</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0171791785300876</v>
+        <v>0.01693376169394348</v>
       </c>
       <c r="W71">
-        <v>0.2317491497026054</v>
+        <v>0.2318070189925681</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.09041672910572429</v>
+        <v>0.08912506154707101</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.23926466579652</v>
+        <v>0.24116466579652</v>
       </c>
       <c r="C72">
-        <v>-12.01457845168033</v>
+        <v>-12.46829138357624</v>
       </c>
       <c r="D72">
-        <v>11.07542154831967</v>
+        <v>10.96770861642377</v>
       </c>
       <c r="E72">
-        <v>24.22</v>
+        <v>24.566</v>
       </c>
       <c r="F72">
-        <v>24.22</v>
+        <v>24.566</v>
       </c>
       <c r="G72">
         <v>1.13</v>
@@ -7191,37 +7191,37 @@
         <v>0.509</v>
       </c>
       <c r="M72">
-        <v>5.711076000000001</v>
+        <v>5.7926628</v>
       </c>
       <c r="N72">
-        <v>-5.202076000000001</v>
+        <v>-5.2836628</v>
       </c>
       <c r="O72">
-        <v>-0.9883944400000002</v>
+        <v>-1.003895932</v>
       </c>
       <c r="P72">
-        <v>-4.21368156</v>
+        <v>-4.279766868</v>
       </c>
       <c r="Q72">
-        <v>-3.96568156</v>
+        <v>-4.031766868</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2566658416724077</v>
+        <v>0.2639370775921459</v>
       </c>
       <c r="T72">
-        <v>3.862081943254978</v>
+        <v>3.995257182677564</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01693376169394348</v>
+        <v>0.0166952580081133</v>
       </c>
       <c r="W72">
-        <v>0.2318070189925681</v>
+        <v>0.2318632581616869</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.08912506154707101</v>
+        <v>0.08786977899007009</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.24116466579652</v>
+        <v>0.24306466579652</v>
       </c>
       <c r="C73">
-        <v>-12.46829138357623</v>
+        <v>-12.91992939171653</v>
       </c>
       <c r="D73">
-        <v>10.96770861642377</v>
+        <v>10.86207060828347</v>
       </c>
       <c r="E73">
-        <v>24.566</v>
+        <v>24.912</v>
       </c>
       <c r="F73">
-        <v>24.566</v>
+        <v>24.912</v>
       </c>
       <c r="G73">
         <v>1.13</v>
@@ -7273,37 +7273,37 @@
         <v>0.509</v>
       </c>
       <c r="M73">
-        <v>5.7926628</v>
+        <v>5.8742496</v>
       </c>
       <c r="N73">
-        <v>-5.283662799999999</v>
+        <v>-5.365249599999999</v>
       </c>
       <c r="O73">
-        <v>-1.003895932</v>
+        <v>-1.019397424</v>
       </c>
       <c r="P73">
-        <v>-4.279766867999999</v>
+        <v>-4.345852175999999</v>
       </c>
       <c r="Q73">
-        <v>-4.031766867999999</v>
+        <v>-4.097852175999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2639370775921459</v>
+        <v>0.2717276875061511</v>
       </c>
       <c r="T73">
-        <v>3.995257182677563</v>
+        <v>4.137944939201762</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0166952580081133</v>
+        <v>0.01646337942466728</v>
       </c>
       <c r="W73">
-        <v>0.2318632581616869</v>
+        <v>0.2319179351316635</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.08786977899007009</v>
+        <v>0.08664936539298573</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.24306466579652</v>
+        <v>0.24496466579652</v>
       </c>
       <c r="C74">
-        <v>-12.91992939171653</v>
+        <v>-13.36955185945297</v>
       </c>
       <c r="D74">
-        <v>10.86207060828347</v>
+        <v>10.75844814054703</v>
       </c>
       <c r="E74">
-        <v>24.912</v>
+        <v>25.258</v>
       </c>
       <c r="F74">
-        <v>24.912</v>
+        <v>25.258</v>
       </c>
       <c r="G74">
         <v>1.13</v>
@@ -7355,37 +7355,37 @@
         <v>0.509</v>
       </c>
       <c r="M74">
-        <v>5.8742496</v>
+        <v>5.9558364</v>
       </c>
       <c r="N74">
-        <v>-5.365249599999999</v>
+        <v>-5.4468364</v>
       </c>
       <c r="O74">
-        <v>-1.019397424</v>
+        <v>-1.034898916</v>
       </c>
       <c r="P74">
-        <v>-4.345852175999999</v>
+        <v>-4.411937483999999</v>
       </c>
       <c r="Q74">
-        <v>-4.097852175999999</v>
+        <v>-4.163937483999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2717276875061511</v>
+        <v>0.2800953796360085</v>
       </c>
       <c r="T74">
-        <v>4.137944939201762</v>
+        <v>4.291202159172196</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01646337942466728</v>
+        <v>0.01623785367912389</v>
       </c>
       <c r="W74">
-        <v>0.2319179351316635</v>
+        <v>0.2319711141024626</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.08664936539298573</v>
+        <v>0.0854623877848627</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.24496466579652</v>
+        <v>0.24686466579652</v>
       </c>
       <c r="C75">
-        <v>-13.36955185945297</v>
+        <v>-13.81721592551878</v>
       </c>
       <c r="D75">
-        <v>10.75844814054703</v>
+        <v>10.65678407448122</v>
       </c>
       <c r="E75">
-        <v>25.258</v>
+        <v>25.604</v>
       </c>
       <c r="F75">
-        <v>25.258</v>
+        <v>25.604</v>
       </c>
       <c r="G75">
         <v>1.13</v>
@@ -7437,37 +7437,37 @@
         <v>0.509</v>
       </c>
       <c r="M75">
-        <v>5.9558364</v>
+        <v>6.0374232</v>
       </c>
       <c r="N75">
-        <v>-5.4468364</v>
+        <v>-5.5284232</v>
       </c>
       <c r="O75">
-        <v>-1.034898916</v>
+        <v>-1.050400408</v>
       </c>
       <c r="P75">
-        <v>-4.411937483999999</v>
+        <v>-4.478022792</v>
       </c>
       <c r="Q75">
-        <v>-4.163937483999999</v>
+        <v>-4.230022792</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2800953796360085</v>
+        <v>0.2891067403912396</v>
       </c>
       <c r="T75">
-        <v>4.291202159172196</v>
+        <v>4.456248396063436</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01623785367912389</v>
+        <v>0.0160184232240006</v>
       </c>
       <c r="W75">
-        <v>0.2319711141024626</v>
+        <v>0.2320228558037807</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0854623877848627</v>
+        <v>0.08430749065263476</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.24686466579652</v>
+        <v>0.24876466579652</v>
       </c>
       <c r="C76">
-        <v>-13.81721592551878</v>
+        <v>-14.26297658909071</v>
       </c>
       <c r="D76">
-        <v>10.65678407448122</v>
+        <v>10.55702341090929</v>
       </c>
       <c r="E76">
-        <v>25.604</v>
+        <v>25.95</v>
       </c>
       <c r="F76">
-        <v>25.604</v>
+        <v>25.95</v>
       </c>
       <c r="G76">
         <v>1.13</v>
@@ -7519,37 +7519,37 @@
         <v>0.509</v>
       </c>
       <c r="M76">
-        <v>6.0374232</v>
+        <v>6.119010000000001</v>
       </c>
       <c r="N76">
-        <v>-5.5284232</v>
+        <v>-5.610010000000001</v>
       </c>
       <c r="O76">
-        <v>-1.050400408</v>
+        <v>-1.0659019</v>
       </c>
       <c r="P76">
-        <v>-4.478022792</v>
+        <v>-4.544108100000001</v>
       </c>
       <c r="Q76">
-        <v>-4.230022792</v>
+        <v>-4.296108100000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2891067403912396</v>
+        <v>0.2988390100068892</v>
       </c>
       <c r="T76">
-        <v>4.456248396063436</v>
+        <v>4.634498331905974</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0160184232240006</v>
+        <v>0.01580484424768059</v>
       </c>
       <c r="W76">
-        <v>0.2320228558037807</v>
+        <v>0.2320732177263969</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.08430749065263476</v>
+        <v>0.08318339077726633</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.24876466579652</v>
+        <v>0.25066466579652</v>
       </c>
       <c r="C77">
-        <v>-14.26297658909071</v>
+        <v>-14.70688680900463</v>
       </c>
       <c r="D77">
-        <v>10.55702341090929</v>
+        <v>10.45911319099538</v>
       </c>
       <c r="E77">
-        <v>25.95</v>
+        <v>26.296</v>
       </c>
       <c r="F77">
-        <v>25.95</v>
+        <v>26.296</v>
       </c>
       <c r="G77">
         <v>1.13</v>
@@ -7601,37 +7601,37 @@
         <v>0.509</v>
       </c>
       <c r="M77">
-        <v>6.119010000000001</v>
+        <v>6.200596800000001</v>
       </c>
       <c r="N77">
-        <v>-5.610010000000001</v>
+        <v>-5.691596800000001</v>
       </c>
       <c r="O77">
-        <v>-1.0659019</v>
+        <v>-1.081403392</v>
       </c>
       <c r="P77">
-        <v>-4.544108100000001</v>
+        <v>-4.610193408000001</v>
       </c>
       <c r="Q77">
-        <v>-4.296108100000001</v>
+        <v>-4.362193408</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2988390100068892</v>
+        <v>0.3093823020905097</v>
       </c>
       <c r="T77">
-        <v>4.634498331905974</v>
+        <v>4.827602429068723</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01580484424768059</v>
+        <v>0.01559688577073742</v>
       </c>
       <c r="W77">
-        <v>0.2320732177263969</v>
+        <v>0.2321222543352601</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.08318339077726633</v>
+        <v>0.08208887247756547</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.25066466579652</v>
+        <v>0.25256466579652</v>
       </c>
       <c r="C78">
-        <v>-14.70688680900463</v>
+        <v>-15.14899759750099</v>
       </c>
       <c r="D78">
-        <v>10.45911319099538</v>
+        <v>10.36300240249901</v>
       </c>
       <c r="E78">
-        <v>26.296</v>
+        <v>26.642</v>
       </c>
       <c r="F78">
-        <v>26.296</v>
+        <v>26.642</v>
       </c>
       <c r="G78">
         <v>1.13</v>
@@ -7683,37 +7683,37 @@
         <v>0.509</v>
       </c>
       <c r="M78">
-        <v>6.200596800000001</v>
+        <v>6.282183600000001</v>
       </c>
       <c r="N78">
-        <v>-5.691596800000001</v>
+        <v>-5.7731836</v>
       </c>
       <c r="O78">
-        <v>-1.081403392</v>
+        <v>-1.096904884</v>
       </c>
       <c r="P78">
-        <v>-4.610193408000001</v>
+        <v>-4.676278716000001</v>
       </c>
       <c r="Q78">
-        <v>-4.362193408</v>
+        <v>-4.428278716</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3093823020905097</v>
+        <v>0.3208424021814014</v>
       </c>
       <c r="T78">
-        <v>4.827602429068723</v>
+        <v>5.03749818685432</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01559688577073742</v>
+        <v>0.0153943288126759</v>
       </c>
       <c r="W78">
-        <v>0.2321222543352601</v>
+        <v>0.232170017265971</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.08208887247756547</v>
+        <v>0.08102278322460998</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.25256466579652</v>
+        <v>0.25446466579652</v>
       </c>
       <c r="C79">
-        <v>-15.14899759750099</v>
+        <v>-15.58935810884865</v>
       </c>
       <c r="D79">
-        <v>10.36300240249901</v>
+        <v>10.26864189115135</v>
       </c>
       <c r="E79">
-        <v>26.642</v>
+        <v>26.988</v>
       </c>
       <c r="F79">
-        <v>26.642</v>
+        <v>26.988</v>
       </c>
       <c r="G79">
         <v>1.13</v>
@@ -7765,37 +7765,37 @@
         <v>0.509</v>
       </c>
       <c r="M79">
-        <v>6.282183600000001</v>
+        <v>6.363770400000001</v>
       </c>
       <c r="N79">
-        <v>-5.7731836</v>
+        <v>-5.8547704</v>
       </c>
       <c r="O79">
-        <v>-1.096904884</v>
+        <v>-1.112406376</v>
       </c>
       <c r="P79">
-        <v>-4.676278716000001</v>
+        <v>-4.742364024</v>
       </c>
       <c r="Q79">
-        <v>-4.428278716</v>
+        <v>-4.494364024</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3208424021814014</v>
+        <v>0.3333443295532832</v>
       </c>
       <c r="T79">
-        <v>5.03749818685432</v>
+        <v>5.266475377165879</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0153943288126759</v>
+        <v>0.0151969656227698</v>
       </c>
       <c r="W79">
-        <v>0.232170017265971</v>
+        <v>0.2322165555061509</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.08102278322460998</v>
+        <v>0.07998402959352524</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.25446466579652</v>
+        <v>0.25636466579652</v>
       </c>
       <c r="C80">
-        <v>-15.58935810884865</v>
+        <v>-16.02801572317052</v>
       </c>
       <c r="D80">
-        <v>10.26864189115135</v>
+        <v>10.17598427682948</v>
       </c>
       <c r="E80">
-        <v>26.988</v>
+        <v>27.334</v>
       </c>
       <c r="F80">
-        <v>26.988</v>
+        <v>27.334</v>
       </c>
       <c r="G80">
         <v>1.13</v>
@@ -7847,37 +7847,37 @@
         <v>0.509</v>
       </c>
       <c r="M80">
-        <v>6.363770400000001</v>
+        <v>6.445357200000001</v>
       </c>
       <c r="N80">
-        <v>-5.8547704</v>
+        <v>-5.936357200000001</v>
       </c>
       <c r="O80">
-        <v>-1.112406376</v>
+        <v>-1.127907868</v>
       </c>
       <c r="P80">
-        <v>-4.742364024</v>
+        <v>-4.808449332</v>
       </c>
       <c r="Q80">
-        <v>-4.494364024</v>
+        <v>-4.560449332</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3333443295532832</v>
+        <v>0.3470369166748682</v>
       </c>
       <c r="T80">
-        <v>5.266475377165879</v>
+        <v>5.517259918935684</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0151969656227698</v>
+        <v>0.01500459896931701</v>
       </c>
       <c r="W80">
-        <v>0.2322165555061509</v>
+        <v>0.232261915563035</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07998402959352524</v>
+        <v>0.07897157352272122</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.25636466579652</v>
+        <v>0.25826466579652</v>
       </c>
       <c r="C81">
-        <v>-16.02801572317052</v>
+        <v>-16.46501612577155</v>
       </c>
       <c r="D81">
-        <v>10.17598427682948</v>
+        <v>10.08498387422845</v>
       </c>
       <c r="E81">
-        <v>27.334</v>
+        <v>27.68</v>
       </c>
       <c r="F81">
-        <v>27.334</v>
+        <v>27.68</v>
       </c>
       <c r="G81">
         <v>1.13</v>
@@ -7929,37 +7929,37 @@
         <v>0.509</v>
       </c>
       <c r="M81">
-        <v>6.445357200000001</v>
+        <v>6.526944000000001</v>
       </c>
       <c r="N81">
-        <v>-5.936357200000001</v>
+        <v>-6.017944000000001</v>
       </c>
       <c r="O81">
-        <v>-1.127907868</v>
+        <v>-1.14340936</v>
       </c>
       <c r="P81">
-        <v>-4.808449332</v>
+        <v>-4.87453464</v>
       </c>
       <c r="Q81">
-        <v>-4.560449332</v>
+        <v>-4.62653464</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3470369166748682</v>
+        <v>0.3620987625086116</v>
       </c>
       <c r="T81">
-        <v>5.517259918935684</v>
+        <v>5.793122914882468</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01500459896931701</v>
+        <v>0.01481704148220055</v>
       </c>
       <c r="W81">
-        <v>0.232261915563035</v>
+        <v>0.2323061416184971</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07897157352272122</v>
+        <v>0.07798442885368717</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.25826466579652</v>
+        <v>0.26016466579652</v>
       </c>
       <c r="C82">
-        <v>-16.46501612577155</v>
+        <v>-16.90040338224796</v>
       </c>
       <c r="D82">
-        <v>10.08498387422845</v>
+        <v>9.995596617752041</v>
       </c>
       <c r="E82">
-        <v>27.68</v>
+        <v>28.026</v>
       </c>
       <c r="F82">
-        <v>27.68</v>
+        <v>28.026</v>
       </c>
       <c r="G82">
         <v>1.13</v>
@@ -8011,37 +8011,37 @@
         <v>0.509</v>
       </c>
       <c r="M82">
-        <v>6.526944000000001</v>
+        <v>6.608530800000001</v>
       </c>
       <c r="N82">
-        <v>-6.017944000000001</v>
+        <v>-6.099530800000001</v>
       </c>
       <c r="O82">
-        <v>-1.14340936</v>
+        <v>-1.158910852</v>
       </c>
       <c r="P82">
-        <v>-4.87453464</v>
+        <v>-4.940619948000001</v>
       </c>
       <c r="Q82">
-        <v>-4.62653464</v>
+        <v>-4.692619948000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3620987625086116</v>
+        <v>0.3787460657985385</v>
       </c>
       <c r="T82">
-        <v>5.793122914882468</v>
+        <v>6.098024120928914</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01481704148220055</v>
+        <v>0.01463411504414869</v>
       </c>
       <c r="W82">
-        <v>0.2323061416184971</v>
+        <v>0.2323492756725898</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.07798442885368717</v>
+        <v>0.07702165812709838</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.26016466579652</v>
+        <v>0.26206466579652</v>
       </c>
       <c r="C83">
-        <v>-16.90040338224796</v>
+        <v>-17.33422000963728</v>
       </c>
       <c r="D83">
-        <v>9.995596617752041</v>
+        <v>9.907779990362723</v>
       </c>
       <c r="E83">
-        <v>28.026</v>
+        <v>28.372</v>
       </c>
       <c r="F83">
-        <v>28.026</v>
+        <v>28.372</v>
       </c>
       <c r="G83">
         <v>1.13</v>
@@ -8093,37 +8093,37 @@
         <v>0.509</v>
       </c>
       <c r="M83">
-        <v>6.608530800000001</v>
+        <v>6.690117600000001</v>
       </c>
       <c r="N83">
-        <v>-6.099530800000001</v>
+        <v>-6.1811176</v>
       </c>
       <c r="O83">
-        <v>-1.158910852</v>
+        <v>-1.174412344</v>
       </c>
       <c r="P83">
-        <v>-4.940619948000001</v>
+        <v>-5.006705256</v>
       </c>
       <c r="Q83">
-        <v>-4.692619948000001</v>
+        <v>-4.758705256</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3787460657985385</v>
+        <v>0.3972430694540129</v>
       </c>
       <c r="T83">
-        <v>6.098024120928914</v>
+        <v>6.436803238758298</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01463411504414869</v>
+        <v>0.01445565022653712</v>
       </c>
       <c r="W83">
-        <v>0.2323492756725898</v>
+        <v>0.2323913576765825</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07702165812709838</v>
+        <v>0.07608236961335335</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.26206466579652</v>
+        <v>0.26396466579652</v>
       </c>
       <c r="C84">
-        <v>-17.33422000963728</v>
+        <v>-17.76650704385045</v>
       </c>
       <c r="D84">
-        <v>9.907779990362723</v>
+        <v>9.82149295614955</v>
       </c>
       <c r="E84">
-        <v>28.372</v>
+        <v>28.718</v>
       </c>
       <c r="F84">
-        <v>28.372</v>
+        <v>28.718</v>
       </c>
       <c r="G84">
         <v>1.13</v>
@@ -8175,37 +8175,37 @@
         <v>0.509</v>
       </c>
       <c r="M84">
-        <v>6.690117600000001</v>
+        <v>6.771704400000001</v>
       </c>
       <c r="N84">
-        <v>-6.1811176</v>
+        <v>-6.262704400000001</v>
       </c>
       <c r="O84">
-        <v>-1.174412344</v>
+        <v>-1.189913836</v>
       </c>
       <c r="P84">
-        <v>-5.006705256</v>
+        <v>-5.072790564</v>
       </c>
       <c r="Q84">
-        <v>-4.758705256</v>
+        <v>-4.824790564</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3972430694540129</v>
+        <v>0.4179161911866019</v>
       </c>
       <c r="T84">
-        <v>6.436803238758298</v>
+        <v>6.81543872339114</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01445565022653712</v>
+        <v>0.01428148576597643</v>
       </c>
       <c r="W84">
-        <v>0.2323913576765825</v>
+        <v>0.2324324256563828</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.07608236961335335</v>
+        <v>0.07516571455777077</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.26396466579652</v>
+        <v>0.26586466579652</v>
       </c>
       <c r="C85">
-        <v>-17.76650704385045</v>
+        <v>-18.19730410361078</v>
       </c>
       <c r="D85">
-        <v>9.82149295614955</v>
+        <v>9.73669589638922</v>
       </c>
       <c r="E85">
-        <v>28.718</v>
+        <v>29.064</v>
       </c>
       <c r="F85">
-        <v>28.718</v>
+        <v>29.064</v>
       </c>
       <c r="G85">
         <v>1.13</v>
@@ -8257,37 +8257,37 @@
         <v>0.509</v>
       </c>
       <c r="M85">
-        <v>6.771704400000001</v>
+        <v>6.853291200000001</v>
       </c>
       <c r="N85">
-        <v>-6.262704400000001</v>
+        <v>-6.344291200000001</v>
       </c>
       <c r="O85">
-        <v>-1.189913836</v>
+        <v>-1.205415328</v>
       </c>
       <c r="P85">
-        <v>-5.072790564</v>
+        <v>-5.138875872000001</v>
       </c>
       <c r="Q85">
-        <v>-4.824790564</v>
+        <v>-4.890875872000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4179161911866019</v>
+        <v>0.4411734531357647</v>
       </c>
       <c r="T85">
-        <v>6.81543872339114</v>
+        <v>7.241403643603088</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01428148576597643</v>
+        <v>0.01411146807828624</v>
       </c>
       <c r="W85">
-        <v>0.2324324256563828</v>
+        <v>0.2324725158271401</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.07516571455777077</v>
+        <v>0.07427088462255915</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.26586466579652</v>
+        <v>0.26776466579652</v>
       </c>
       <c r="C86">
-        <v>-18.19730410361078</v>
+        <v>-18.62664945110901</v>
       </c>
       <c r="D86">
-        <v>9.73669589638922</v>
+        <v>9.653350548890993</v>
       </c>
       <c r="E86">
-        <v>29.064</v>
+        <v>29.41</v>
       </c>
       <c r="F86">
-        <v>29.064</v>
+        <v>29.41</v>
       </c>
       <c r="G86">
         <v>1.13</v>
@@ -8339,37 +8339,37 @@
         <v>0.509</v>
       </c>
       <c r="M86">
-        <v>6.8532912</v>
+        <v>6.934878</v>
       </c>
       <c r="N86">
-        <v>-6.3442912</v>
+        <v>-6.425878</v>
       </c>
       <c r="O86">
-        <v>-1.205415328</v>
+        <v>-1.22091682</v>
       </c>
       <c r="P86">
-        <v>-5.138875872</v>
+        <v>-5.20496118</v>
       </c>
       <c r="Q86">
-        <v>-4.890875872</v>
+        <v>-4.95696118</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4411734531357644</v>
+        <v>0.4675316833448153</v>
       </c>
       <c r="T86">
-        <v>7.241403643603083</v>
+        <v>7.724163886509954</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01411146807828624</v>
+        <v>0.01394545080677699</v>
       </c>
       <c r="W86">
-        <v>0.2324725158271401</v>
+        <v>0.232511662699762</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.07427088462255915</v>
+        <v>0.07339710950935263</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.26776466579652</v>
+        <v>0.26966466579652</v>
       </c>
       <c r="C87">
-        <v>-18.62664945110901</v>
+        <v>-19.05458004956962</v>
       </c>
       <c r="D87">
-        <v>9.653350548890993</v>
+        <v>9.571419950430386</v>
       </c>
       <c r="E87">
-        <v>29.41</v>
+        <v>29.756</v>
       </c>
       <c r="F87">
-        <v>29.41</v>
+        <v>29.756</v>
       </c>
       <c r="G87">
         <v>1.13</v>
@@ -8421,37 +8421,37 @@
         <v>0.509</v>
       </c>
       <c r="M87">
-        <v>6.934878</v>
+        <v>7.016464800000001</v>
       </c>
       <c r="N87">
-        <v>-6.425878</v>
+        <v>-6.5074648</v>
       </c>
       <c r="O87">
-        <v>-1.22091682</v>
+        <v>-1.236418312</v>
       </c>
       <c r="P87">
-        <v>-5.20496118</v>
+        <v>-5.271046488</v>
       </c>
       <c r="Q87">
-        <v>-4.95696118</v>
+        <v>-5.023046487999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4675316833448153</v>
+        <v>0.4976553750123022</v>
       </c>
       <c r="T87">
-        <v>7.724163886509954</v>
+        <v>8.275889878403524</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01394545080677699</v>
+        <v>0.01378329440204702</v>
       </c>
       <c r="W87">
-        <v>0.232511662699762</v>
+        <v>0.2325498991799973</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.07339710950935263</v>
+        <v>0.07254365474761593</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.26966466579652</v>
+        <v>0.2715646657965199</v>
       </c>
       <c r="C88">
-        <v>-19.05458004956962</v>
+        <v>-19.48113161791029</v>
       </c>
       <c r="D88">
-        <v>9.571419950430386</v>
+        <v>9.490868382089712</v>
       </c>
       <c r="E88">
-        <v>29.756</v>
+        <v>30.102</v>
       </c>
       <c r="F88">
-        <v>29.756</v>
+        <v>30.102</v>
       </c>
       <c r="G88">
         <v>1.13</v>
@@ -8503,37 +8503,37 @@
         <v>0.509</v>
       </c>
       <c r="M88">
-        <v>7.016464800000001</v>
+        <v>7.098051600000001</v>
       </c>
       <c r="N88">
-        <v>-6.5074648</v>
+        <v>-6.5890516</v>
       </c>
       <c r="O88">
-        <v>-1.236418312</v>
+        <v>-1.251919804</v>
       </c>
       <c r="P88">
-        <v>-5.271046488</v>
+        <v>-5.337131796</v>
       </c>
       <c r="Q88">
-        <v>-5.023046487999999</v>
+        <v>-5.089131796</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4976553750123022</v>
+        <v>0.5324134807824792</v>
       </c>
       <c r="T88">
-        <v>8.275889878403524</v>
+        <v>8.91249679212687</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01378329440204702</v>
+        <v>0.01362486573075913</v>
       </c>
       <c r="W88">
-        <v>0.2325498991799973</v>
+        <v>0.232587256660687</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.07254365474761593</v>
+        <v>0.07170981963557443</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2715646657965199</v>
+        <v>0.27346466579652</v>
       </c>
       <c r="C89">
-        <v>-19.48113161791029</v>
+        <v>-19.90633868266441</v>
       </c>
       <c r="D89">
-        <v>9.490868382089712</v>
+        <v>9.411661317335589</v>
       </c>
       <c r="E89">
-        <v>30.102</v>
+        <v>30.448</v>
       </c>
       <c r="F89">
-        <v>30.102</v>
+        <v>30.448</v>
       </c>
       <c r="G89">
         <v>1.13</v>
@@ -8585,37 +8585,37 @@
         <v>0.509</v>
       </c>
       <c r="M89">
-        <v>7.098051600000001</v>
+        <v>7.1796384</v>
       </c>
       <c r="N89">
-        <v>-6.5890516</v>
+        <v>-6.6706384</v>
       </c>
       <c r="O89">
-        <v>-1.251919804</v>
+        <v>-1.267421296</v>
       </c>
       <c r="P89">
-        <v>-5.337131796</v>
+        <v>-5.403217103999999</v>
       </c>
       <c r="Q89">
-        <v>-5.089131796</v>
+        <v>-5.155217103999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5324134807824792</v>
+        <v>0.5729646041810192</v>
       </c>
       <c r="T89">
-        <v>8.91249679212687</v>
+        <v>9.655204858137445</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01362486573075913</v>
+        <v>0.01347003771109141</v>
       </c>
       <c r="W89">
-        <v>0.232587256660687</v>
+        <v>0.2326237651077246</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.07170981963557443</v>
+        <v>0.07089493532153379</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.27346466579652</v>
+        <v>0.27536466579652</v>
       </c>
       <c r="C90">
-        <v>-19.90633868266441</v>
+        <v>-20.33023462732511</v>
       </c>
       <c r="D90">
-        <v>9.411661317335589</v>
+        <v>9.333765372674891</v>
       </c>
       <c r="E90">
-        <v>30.448</v>
+        <v>30.794</v>
       </c>
       <c r="F90">
-        <v>30.448</v>
+        <v>30.794</v>
       </c>
       <c r="G90">
         <v>1.13</v>
@@ -8667,37 +8667,37 @@
         <v>0.509</v>
       </c>
       <c r="M90">
-        <v>7.1796384</v>
+        <v>7.2612252</v>
       </c>
       <c r="N90">
-        <v>-6.6706384</v>
+        <v>-6.7522252</v>
       </c>
       <c r="O90">
-        <v>-1.267421296</v>
+        <v>-1.282922788</v>
       </c>
       <c r="P90">
-        <v>-5.403217103999999</v>
+        <v>-5.469302411999999</v>
       </c>
       <c r="Q90">
-        <v>-5.155217103999999</v>
+        <v>-5.221302411999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5729646041810192</v>
+        <v>0.6208886591065663</v>
       </c>
       <c r="T90">
-        <v>9.655204858137445</v>
+        <v>10.53295075433176</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01347003771109141</v>
+        <v>0.01331868897276454</v>
       </c>
       <c r="W90">
-        <v>0.2326237651077246</v>
+        <v>0.2326594531402221</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.07089493532153379</v>
+        <v>0.0700983630145503</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.27536466579652</v>
+        <v>0.27726466579652</v>
       </c>
       <c r="C91">
-        <v>-20.33023462732511</v>
+        <v>-20.75285173925904</v>
       </c>
       <c r="D91">
-        <v>9.333765372674891</v>
+        <v>9.257148260740959</v>
       </c>
       <c r="E91">
-        <v>30.794</v>
+        <v>31.14</v>
       </c>
       <c r="F91">
-        <v>30.794</v>
+        <v>31.14</v>
       </c>
       <c r="G91">
         <v>1.13</v>
@@ -8749,37 +8749,37 @@
         <v>0.509</v>
       </c>
       <c r="M91">
-        <v>7.2612252</v>
+        <v>7.342812</v>
       </c>
       <c r="N91">
-        <v>-6.7522252</v>
+        <v>-6.833812</v>
       </c>
       <c r="O91">
-        <v>-1.282922788</v>
+        <v>-1.29842428</v>
       </c>
       <c r="P91">
-        <v>-5.469302411999999</v>
+        <v>-5.53538772</v>
       </c>
       <c r="Q91">
-        <v>-5.221302411999999</v>
+        <v>-5.28738772</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6208886591065663</v>
+        <v>0.6783975250172231</v>
       </c>
       <c r="T91">
-        <v>10.53295075433176</v>
+        <v>11.58624582976493</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01331868897276454</v>
+        <v>0.01317070353973382</v>
       </c>
       <c r="W91">
-        <v>0.2326594531402221</v>
+        <v>0.2326943481053308</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.0700983630145503</v>
+        <v>0.06931949231438861</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.27726466579652</v>
+        <v>0.27916466579652</v>
       </c>
       <c r="C92">
-        <v>-20.75285173925904</v>
+        <v>-21.17422125432841</v>
       </c>
       <c r="D92">
-        <v>9.257148260740959</v>
+        <v>9.181778745671593</v>
       </c>
       <c r="E92">
-        <v>31.14</v>
+        <v>31.486</v>
       </c>
       <c r="F92">
-        <v>31.14</v>
+        <v>31.486</v>
       </c>
       <c r="G92">
         <v>1.13</v>
@@ -8831,37 +8831,37 @@
         <v>0.509</v>
       </c>
       <c r="M92">
-        <v>7.342812</v>
+        <v>7.424398800000001</v>
       </c>
       <c r="N92">
-        <v>-6.833812</v>
+        <v>-6.9153988</v>
       </c>
       <c r="O92">
-        <v>-1.29842428</v>
+        <v>-1.313925772</v>
       </c>
       <c r="P92">
-        <v>-5.53538772</v>
+        <v>-5.601473028</v>
       </c>
       <c r="Q92">
-        <v>-5.28738772</v>
+        <v>-5.353473028</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6783975250172231</v>
+        <v>0.7486861389080257</v>
       </c>
       <c r="T92">
-        <v>11.58624582976493</v>
+        <v>12.8736064775166</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01317070353973382</v>
+        <v>0.01302597053380268</v>
       </c>
       <c r="W92">
-        <v>0.2326943481053308</v>
+        <v>0.2327284761481293</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06931949231438861</v>
+        <v>0.06855773965159306</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.27916466579652</v>
+        <v>0.28106466579652</v>
       </c>
       <c r="C93">
-        <v>-21.17422125432841</v>
+        <v>-21.59437339935075</v>
       </c>
       <c r="D93">
-        <v>9.181778745671593</v>
+        <v>9.107626600649253</v>
       </c>
       <c r="E93">
-        <v>31.486</v>
+        <v>31.832</v>
       </c>
       <c r="F93">
-        <v>31.486</v>
+        <v>31.832</v>
       </c>
       <c r="G93">
         <v>1.13</v>
@@ -8913,37 +8913,37 @@
         <v>0.509</v>
       </c>
       <c r="M93">
-        <v>7.424398800000001</v>
+        <v>7.505985600000002</v>
       </c>
       <c r="N93">
-        <v>-6.9153988</v>
+        <v>-6.996985600000001</v>
       </c>
       <c r="O93">
-        <v>-1.313925772</v>
+        <v>-1.329427264</v>
       </c>
       <c r="P93">
-        <v>-5.601473028</v>
+        <v>-5.667558336000001</v>
       </c>
       <c r="Q93">
-        <v>-5.353473028</v>
+        <v>-5.419558336000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7486861389080257</v>
+        <v>0.8365469062715292</v>
       </c>
       <c r="T93">
-        <v>12.8736064775166</v>
+        <v>14.48280728720617</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01302597053380268</v>
+        <v>0.0128843838975657</v>
       </c>
       <c r="W93">
-        <v>0.2327284761481293</v>
+        <v>0.232761862276954</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06855773965159306</v>
+        <v>0.06781254682929316</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.28106466579652</v>
+        <v>0.28296466579652</v>
       </c>
       <c r="C94">
-        <v>-21.59437339935075</v>
+        <v>-22.01333743251782</v>
       </c>
       <c r="D94">
-        <v>9.107626600649253</v>
+        <v>9.034662567482185</v>
       </c>
       <c r="E94">
-        <v>31.832</v>
+        <v>32.178</v>
       </c>
       <c r="F94">
-        <v>31.832</v>
+        <v>32.178</v>
       </c>
       <c r="G94">
         <v>1.13</v>
@@ -8995,37 +8995,37 @@
         <v>0.509</v>
       </c>
       <c r="M94">
-        <v>7.505985600000002</v>
+        <v>7.587572400000002</v>
       </c>
       <c r="N94">
-        <v>-6.996985600000001</v>
+        <v>-7.078572400000001</v>
       </c>
       <c r="O94">
-        <v>-1.329427264</v>
+        <v>-1.344928756</v>
       </c>
       <c r="P94">
-        <v>-5.667558336000001</v>
+        <v>-5.733643644000001</v>
       </c>
       <c r="Q94">
-        <v>-5.419558336000001</v>
+        <v>-5.485643644</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8365469062715292</v>
+        <v>0.9495107500246051</v>
       </c>
       <c r="T94">
-        <v>14.48280728720617</v>
+        <v>16.55177975680706</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0128843838975657</v>
+        <v>0.01274584213522628</v>
       </c>
       <c r="W94">
-        <v>0.232761862276954</v>
+        <v>0.2327945304245137</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06781254682929316</v>
+        <v>0.06708337965908573</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.28296466579652</v>
+        <v>0.28486466579652</v>
       </c>
       <c r="C95">
-        <v>-22.01333743251782</v>
+        <v>-22.43114168188701</v>
       </c>
       <c r="D95">
-        <v>9.034662567482185</v>
+        <v>8.962858318112993</v>
       </c>
       <c r="E95">
-        <v>32.178</v>
+        <v>32.524</v>
       </c>
       <c r="F95">
-        <v>32.178</v>
+        <v>32.524</v>
       </c>
       <c r="G95">
         <v>1.13</v>
@@ -9077,37 +9077,37 @@
         <v>0.509</v>
       </c>
       <c r="M95">
-        <v>7.587572400000002</v>
+        <v>7.6691592</v>
       </c>
       <c r="N95">
-        <v>-7.078572400000001</v>
+        <v>-7.1601592</v>
       </c>
       <c r="O95">
-        <v>-1.344928756</v>
+        <v>-1.360430248</v>
       </c>
       <c r="P95">
-        <v>-5.733643644000001</v>
+        <v>-5.799728952</v>
       </c>
       <c r="Q95">
-        <v>-5.485643644</v>
+        <v>-5.551728951999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9495107500246051</v>
+        <v>1.10012920836204</v>
       </c>
       <c r="T95">
-        <v>16.55177975680706</v>
+        <v>19.31040971627491</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01274584213522628</v>
+        <v>0.01261024806995792</v>
       </c>
       <c r="W95">
-        <v>0.2327945304245137</v>
+        <v>0.2328265035051039</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06708337965908573</v>
+        <v>0.06636972668398911</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.28486466579652</v>
+        <v>0.28676466579652</v>
       </c>
       <c r="C96">
-        <v>-22.43114168188701</v>
+        <v>-22.84781358205181</v>
       </c>
       <c r="D96">
-        <v>8.962858318112993</v>
+        <v>8.892186417948196</v>
       </c>
       <c r="E96">
-        <v>32.524</v>
+        <v>32.87</v>
       </c>
       <c r="F96">
-        <v>32.524</v>
+        <v>32.87</v>
       </c>
       <c r="G96">
         <v>1.13</v>
@@ -9159,37 +9159,37 @@
         <v>0.509</v>
       </c>
       <c r="M96">
-        <v>7.6691592</v>
+        <v>7.750746000000001</v>
       </c>
       <c r="N96">
-        <v>-7.1601592</v>
+        <v>-7.241746000000001</v>
       </c>
       <c r="O96">
-        <v>-1.360430248</v>
+        <v>-1.37593174</v>
       </c>
       <c r="P96">
-        <v>-5.799728952</v>
+        <v>-5.865814260000001</v>
       </c>
       <c r="Q96">
-        <v>-5.551728951999999</v>
+        <v>-5.61781426</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.10012920836204</v>
+        <v>1.310995050034448</v>
       </c>
       <c r="T96">
-        <v>19.31040971627491</v>
+        <v>23.1724916595299</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01261024806995792</v>
+        <v>0.01247750861658994</v>
       </c>
       <c r="W96">
-        <v>0.2328265035051039</v>
+        <v>0.2328578034682081</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06636972668398911</v>
+        <v>0.0656710979820524</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.28676466579652</v>
+        <v>0.28866466579652</v>
       </c>
       <c r="C97">
-        <v>-22.84781358205181</v>
+        <v>-23.26337970909087</v>
       </c>
       <c r="D97">
-        <v>8.892186417948196</v>
+        <v>8.822620290909132</v>
       </c>
       <c r="E97">
-        <v>32.87</v>
+        <v>33.216</v>
       </c>
       <c r="F97">
-        <v>32.87</v>
+        <v>33.216</v>
       </c>
       <c r="G97">
         <v>1.13</v>
@@ -9241,37 +9241,37 @@
         <v>0.509</v>
       </c>
       <c r="M97">
-        <v>7.750746000000001</v>
+        <v>7.832332800000001</v>
       </c>
       <c r="N97">
-        <v>-7.241746000000001</v>
+        <v>-7.3233328</v>
       </c>
       <c r="O97">
-        <v>-1.37593174</v>
+        <v>-1.391433232</v>
       </c>
       <c r="P97">
-        <v>-5.865814260000001</v>
+        <v>-5.931899568</v>
       </c>
       <c r="Q97">
-        <v>-5.61781426</v>
+        <v>-5.683899568</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.310995050034448</v>
+        <v>1.62729381254306</v>
       </c>
       <c r="T97">
-        <v>23.1724916595299</v>
+        <v>28.96561457441238</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01247750861658994</v>
+        <v>0.01234753456850046</v>
       </c>
       <c r="W97">
-        <v>0.2328578034682081</v>
+        <v>0.2328884513487476</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0656710979820524</v>
+        <v>0.06498702404473933</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.28866466579652</v>
+        <v>0.29056466579652</v>
       </c>
       <c r="C98">
-        <v>-23.26337970909087</v>
+        <v>-23.67786581388944</v>
       </c>
       <c r="D98">
-        <v>8.822620290909132</v>
+        <v>8.754134186110562</v>
       </c>
       <c r="E98">
-        <v>33.216</v>
+        <v>33.562</v>
       </c>
       <c r="F98">
-        <v>33.216</v>
+        <v>33.562</v>
       </c>
       <c r="G98">
         <v>1.13</v>
@@ -9323,37 +9323,37 @@
         <v>0.509</v>
       </c>
       <c r="M98">
-        <v>7.832332800000001</v>
+        <v>7.9139196</v>
       </c>
       <c r="N98">
-        <v>-7.3233328</v>
+        <v>-7.404919599999999</v>
       </c>
       <c r="O98">
-        <v>-1.391433232</v>
+        <v>-1.406934724</v>
       </c>
       <c r="P98">
-        <v>-5.931899568</v>
+        <v>-5.997984875999999</v>
       </c>
       <c r="Q98">
-        <v>-5.683899568</v>
+        <v>-5.749984875999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.627293812543056</v>
+        <v>2.154458416724075</v>
       </c>
       <c r="T98">
-        <v>28.96561457441231</v>
+        <v>38.62081943254974</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01234753456850046</v>
+        <v>0.01222024039769118</v>
       </c>
       <c r="W98">
-        <v>0.2328884513487476</v>
+        <v>0.2329184673142244</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06498702404473933</v>
+        <v>0.0643170547246904</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.29056466579652</v>
+        <v>0.29246466579652</v>
       </c>
       <c r="C99">
-        <v>-23.67786581388944</v>
+        <v>-24.09129685392065</v>
       </c>
       <c r="D99">
-        <v>8.754134186110562</v>
+        <v>8.686703146079351</v>
       </c>
       <c r="E99">
-        <v>33.562</v>
+        <v>33.908</v>
       </c>
       <c r="F99">
-        <v>33.562</v>
+        <v>33.908</v>
       </c>
       <c r="G99">
         <v>1.13</v>
@@ -9405,37 +9405,37 @@
         <v>0.509</v>
       </c>
       <c r="M99">
-        <v>7.9139196</v>
+        <v>7.995506400000001</v>
       </c>
       <c r="N99">
-        <v>-7.404919599999999</v>
+        <v>-7.486506400000001</v>
       </c>
       <c r="O99">
-        <v>-1.406934724</v>
+        <v>-1.422436216</v>
       </c>
       <c r="P99">
-        <v>-5.997984875999999</v>
+        <v>-6.064070184</v>
       </c>
       <c r="Q99">
-        <v>-5.749984875999999</v>
+        <v>-5.816070184</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.154458416724075</v>
+        <v>3.208787625086113</v>
       </c>
       <c r="T99">
-        <v>38.62081943254974</v>
+        <v>57.93122914882462</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01222024039769118</v>
+        <v>0.01209554406710249</v>
       </c>
       <c r="W99">
-        <v>0.2329184673142244</v>
+        <v>0.2329478707089772</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0643170547246904</v>
+        <v>0.06366075824790784</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.29246466579652</v>
+        <v>0.29436466579652</v>
       </c>
       <c r="C100">
-        <v>-24.09129685392065</v>
+        <v>-24.50369702356931</v>
       </c>
       <c r="D100">
-        <v>8.686703146079351</v>
+        <v>8.620302976430693</v>
       </c>
       <c r="E100">
-        <v>33.908</v>
+        <v>34.254</v>
       </c>
       <c r="F100">
-        <v>33.908</v>
+        <v>34.254</v>
       </c>
       <c r="G100">
         <v>1.13</v>
@@ -9487,37 +9487,37 @@
         <v>0.509</v>
       </c>
       <c r="M100">
-        <v>7.995506400000001</v>
+        <v>8.0770932</v>
       </c>
       <c r="N100">
-        <v>-7.486506400000001</v>
+        <v>-7.5680932</v>
       </c>
       <c r="O100">
-        <v>-1.422436216</v>
+        <v>-1.437937708</v>
       </c>
       <c r="P100">
-        <v>-6.064070184</v>
+        <v>-6.130155492</v>
       </c>
       <c r="Q100">
-        <v>-5.816070184</v>
+        <v>-5.882155492</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.208787625086113</v>
+        <v>6.371775250172225</v>
       </c>
       <c r="T100">
-        <v>57.93122914882462</v>
+        <v>115.8624582976492</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01209554406710249</v>
+        <v>0.01197336685430348</v>
       </c>
       <c r="W100">
-        <v>0.2329478707089772</v>
+        <v>0.2329766800957553</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.06366075824790784</v>
+        <v>0.06301772028580777</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.29436466579652</v>
-      </c>
-      <c r="C101">
-        <v>-24.50369702356931</v>
-      </c>
-      <c r="D101">
-        <v>8.620302976430693</v>
-      </c>
-      <c r="E101">
-        <v>34.254</v>
-      </c>
-      <c r="F101">
-        <v>34.254</v>
-      </c>
-      <c r="G101">
-        <v>1.13</v>
-      </c>
-      <c r="H101">
-        <v>34.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.757</v>
-      </c>
-      <c r="K101">
-        <v>0.248</v>
-      </c>
-      <c r="L101">
-        <v>0.509</v>
-      </c>
-      <c r="M101">
-        <v>8.0770932</v>
-      </c>
-      <c r="N101">
-        <v>-7.5680932</v>
-      </c>
-      <c r="O101">
-        <v>-1.437937708</v>
-      </c>
-      <c r="P101">
-        <v>-6.130155492</v>
-      </c>
-      <c r="Q101">
-        <v>-5.882155492</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.371775250172225</v>
-      </c>
-      <c r="T101">
-        <v>115.8624582976492</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01197336685430348</v>
-      </c>
-      <c r="W101">
-        <v>0.2329766800957553</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.06301772028580777</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
